--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AEE5C33-22F5-4F79-BD72-56C947F35F6C}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD5CD0DA-EE9D-4258-93A6-1A755C80F899}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="146">
   <si>
     <t>unidade</t>
   </si>
@@ -68,9 +68,6 @@
     <t>estaleiro maua</t>
   </si>
   <si>
-    <t>staleiro</t>
-  </si>
-  <si>
     <t>TechnipFMC Flexiveis</t>
   </si>
   <si>
@@ -92,18 +89,12 @@
     <t>Triunfo Logística</t>
   </si>
   <si>
-    <t>porto rio</t>
-  </si>
-  <si>
     <t>Baker Hughes Planta de Fluídos - Rio</t>
   </si>
   <si>
     <t>BR RIO</t>
   </si>
   <si>
-    <t>bahia de guabanara</t>
-  </si>
-  <si>
     <t>Porto de imbetiba</t>
   </si>
   <si>
@@ -480,6 +471,9 @@
   </si>
   <si>
     <t>barracuda</t>
+  </si>
+  <si>
+    <t>Fundeio - RIO</t>
   </si>
 </sst>
 </file>
@@ -895,7 +889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.88671875" customWidth="1"/>
@@ -959,12 +953,12 @@
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>-21.8713791957917</v>
@@ -973,15 +967,15 @@
         <v>-41.015639345725504</v>
       </c>
       <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
         <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>-21.870542645313702</v>
@@ -990,15 +984,15 @@
         <v>-41.0185450015653</v>
       </c>
       <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
         <v>12</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>-22.8823482241995</v>
@@ -1007,15 +1001,15 @@
         <v>-43.118152767413797</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>-22.891429443988901</v>
@@ -1024,15 +1018,15 @@
         <v>-43.213849174380996</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>-22.890693724738501</v>
@@ -1041,1484 +1035,1518 @@
         <v>-43.214188120650903</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>-22.838093000000001</v>
+        <v>-22.848614000000001</v>
       </c>
       <c r="C9">
-        <v>-43.140821000000003</v>
+        <v>-43.146186999999998</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B10">
-        <v>-22.3863986649853</v>
+        <v>-22.862100999999999</v>
       </c>
       <c r="C10">
-        <v>-41.768495419907303</v>
+        <v>-43.175891999999997</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>-21.843335</v>
+        <v>-22.838093000000001</v>
       </c>
       <c r="C11">
-        <v>-41.000976999999999</v>
+        <v>-43.140821000000003</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B12">
-        <v>-22.878855000000001</v>
+        <v>-22.3863986649853</v>
       </c>
       <c r="C12">
-        <v>-43.122</v>
+        <v>-41.768495419907303</v>
       </c>
       <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>-21.843335</v>
+      </c>
+      <c r="C13">
+        <v>-41.000976999999999</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" t="s">
         <v>12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13">
-        <v>-25.379460999999999</v>
-      </c>
-      <c r="C13">
-        <v>-44.495949000000003</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B14">
-        <v>-24.629674000000001</v>
+        <v>-22.878855000000001</v>
       </c>
       <c r="C14">
-        <v>-42.264716999999997</v>
+        <v>-43.122</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>33</v>
+      <c r="A15" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B15">
-        <v>-21.943075</v>
+        <v>-25.379460999999999</v>
       </c>
       <c r="C15">
-        <v>-39.759360999999998</v>
+        <v>-44.495949000000003</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B16">
+        <v>-24.629674000000001</v>
+      </c>
+      <c r="C16">
+        <v>-42.264716999999997</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17">
+        <v>-21.943075</v>
+      </c>
+      <c r="C17">
+        <v>-39.759360999999998</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18">
         <f>-24.558464</f>
         <v>-24.558464000000001</v>
       </c>
-      <c r="C16">
+      <c r="C18">
         <v>-42.187762999999997</v>
       </c>
-      <c r="D16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <v>-23.253872999999999</v>
+      </c>
+      <c r="C19">
+        <v>-39.568072999999998</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20">
+        <v>-23.513114999999999</v>
+      </c>
+      <c r="C20">
+        <v>-41.064297000000003</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" t="s">
         <v>36</v>
       </c>
-      <c r="B17">
-        <v>-23.253872999999999</v>
-      </c>
-      <c r="C17">
-        <v>-39.568072999999998</v>
-      </c>
-      <c r="D17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B18">
-        <v>-23.513114999999999</v>
-      </c>
-      <c r="C18">
-        <v>-41.064297000000003</v>
-      </c>
-      <c r="D18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="B21">
+        <v>-21.938911000000001</v>
+      </c>
+      <c r="C21">
+        <v>-39.784574999999997</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" t="s">
         <v>38</v>
       </c>
-      <c r="F18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" t="s">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="B22">
+        <v>-21.214009999999998</v>
+      </c>
+      <c r="C22">
+        <v>-39.997269000000003</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B19">
-        <v>-21.938911000000001</v>
-      </c>
-      <c r="C19">
-        <v>-39.784574999999997</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20">
-        <v>-21.214009999999998</v>
-      </c>
-      <c r="C20">
-        <v>-39.997269000000003</v>
-      </c>
-      <c r="D20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21">
+      <c r="B23">
         <v>-21.33</v>
       </c>
-      <c r="C21">
+      <c r="C23">
         <v>-40.07</v>
       </c>
-      <c r="D21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22">
-        <v>-23.516300000000001</v>
-      </c>
-      <c r="C22">
-        <v>-41.061</v>
-      </c>
-      <c r="D22" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23">
-        <v>-19.86</v>
-      </c>
-      <c r="C23">
-        <v>-39.619999999999997</v>
-      </c>
       <c r="D23" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B24">
-        <v>-22.87</v>
+        <v>-23.516300000000001</v>
       </c>
       <c r="C24">
-        <v>-43.13</v>
+        <v>-41.061</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="G24" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B25">
-        <v>-21.26</v>
+        <v>-19.86</v>
       </c>
       <c r="C25">
-        <v>-40.01</v>
+        <v>-39.619999999999997</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>51</v>
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26">
+        <v>-22.87</v>
+      </c>
+      <c r="C26">
+        <v>-43.13</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B27">
+        <v>-21.26</v>
+      </c>
+      <c r="C27">
+        <v>-40.01</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28">
-        <v>-21.251000000000001</v>
-      </c>
-      <c r="C28">
-        <v>-40.002000000000002</v>
+      <c r="A28" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F28" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29">
-        <v>-21.1599</v>
-      </c>
-      <c r="C29">
-        <v>-39.978400000000001</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>51</v>
+      </c>
+      <c r="B30">
+        <v>-21.251000000000001</v>
+      </c>
+      <c r="C30">
+        <v>-40.002000000000002</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B31">
-        <v>-22.6</v>
+        <v>-21.1599</v>
       </c>
       <c r="C31">
-        <v>-40.26</v>
+        <v>-39.978400000000001</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32">
-        <v>-22.39</v>
-      </c>
-      <c r="C32">
-        <v>-40.1</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F32" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B33">
-        <v>-22.46</v>
+        <v>-22.6</v>
       </c>
       <c r="C33">
-        <v>-40.049999999999997</v>
+        <v>-40.26</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="F33" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B34">
-        <v>-23.133800000000001</v>
+        <v>-22.39</v>
       </c>
       <c r="C34">
-        <v>-41.071300000000001</v>
+        <v>-40.1</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F34" t="s">
-        <v>34</v>
-      </c>
-      <c r="G34" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B35">
-        <v>-22.95</v>
+        <v>-22.46</v>
       </c>
       <c r="C35">
-        <v>-40.72</v>
+        <v>-40.049999999999997</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F35" t="s">
-        <v>34</v>
-      </c>
-      <c r="G35" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B36">
-        <v>-22.0852</v>
+        <v>-23.133800000000001</v>
       </c>
       <c r="C36">
-        <v>-39.827500000000001</v>
+        <v>-41.071300000000001</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F36" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="G36" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B37">
-        <v>-21.882000000000001</v>
+        <v>-22.95</v>
       </c>
       <c r="C37">
-        <v>-39.8598</v>
+        <v>-40.72</v>
       </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E37" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" t="s">
         <v>63</v>
-      </c>
-      <c r="F37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G37" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B38">
-        <v>-22.22</v>
+        <v>-22.0852</v>
       </c>
       <c r="C38">
-        <v>-40.33</v>
+        <v>-39.827500000000001</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="E38" t="s">
+        <v>60</v>
       </c>
       <c r="F38" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B39">
-        <v>-23.317</v>
+        <v>-21.882000000000001</v>
       </c>
       <c r="C39">
-        <v>-41.255200000000002</v>
+        <v>-39.8598</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F39" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G39" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B40">
-        <v>-22.16</v>
+        <v>-22.22</v>
       </c>
       <c r="C40">
-        <v>-40.14</v>
+        <v>-40.33</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="F40" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="B41">
+        <v>-23.317</v>
+      </c>
+      <c r="C41">
+        <v>-41.255200000000002</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>28</v>
+      </c>
+      <c r="E41" t="s">
+        <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="G41" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B42">
-        <v>-21.33</v>
+        <v>-22.16</v>
       </c>
       <c r="C42">
-        <v>-40.01</v>
+        <v>-40.14</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E42" t="s">
+        <v>56</v>
       </c>
       <c r="F42" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D43" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F43" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B44">
-        <v>-21.975999999999999</v>
+        <v>-21.33</v>
       </c>
       <c r="C44">
-        <v>-39.725000000000001</v>
+        <v>-40.01</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F44" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>78</v>
-      </c>
-      <c r="B45">
-        <v>-23.5244</v>
-      </c>
-      <c r="C45">
-        <v>-41.081299999999999</v>
+        <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>47</v>
-      </c>
-      <c r="E45" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F45" t="s">
-        <v>34</v>
-      </c>
-      <c r="G45" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>74</v>
+      </c>
+      <c r="B46">
+        <v>-21.975999999999999</v>
+      </c>
+      <c r="C46">
+        <v>-39.725000000000001</v>
       </c>
       <c r="D46" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F46" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>80</v>
+        <v>75</v>
+      </c>
+      <c r="B47">
+        <v>-23.5244</v>
+      </c>
+      <c r="C47">
+        <v>-41.081299999999999</v>
       </c>
       <c r="D47" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="E47" t="s">
+        <v>45</v>
       </c>
       <c r="F47" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="G47" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>81</v>
-      </c>
-      <c r="B48">
-        <v>-22.37</v>
-      </c>
-      <c r="C48">
-        <v>-40.04</v>
+        <v>76</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50">
+        <v>-22.37</v>
+      </c>
+      <c r="C50">
+        <v>-40.04</v>
+      </c>
+      <c r="D50" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" t="s">
+        <v>80</v>
+      </c>
+      <c r="F51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D52" t="s">
+        <v>80</v>
+      </c>
+      <c r="F52" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>82</v>
       </c>
-      <c r="D49" t="s">
-        <v>83</v>
-      </c>
-      <c r="F49" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" t="s">
-        <v>83</v>
-      </c>
-      <c r="F50" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" t="s">
-        <v>52</v>
-      </c>
-      <c r="F51" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" t="s">
-        <v>52</v>
-      </c>
-      <c r="F52" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>87</v>
-      </c>
       <c r="D53" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F53" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>88</v>
-      </c>
-      <c r="B54">
-        <v>-23.39</v>
-      </c>
-      <c r="C54">
-        <v>-41.4</v>
+        <v>83</v>
       </c>
       <c r="D54" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F54" t="s">
-        <v>34</v>
-      </c>
-      <c r="G54" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D55" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F55" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B56">
+        <v>-23.39</v>
+      </c>
+      <c r="C56">
+        <v>-41.4</v>
+      </c>
+      <c r="D56" t="s">
+        <v>49</v>
+      </c>
+      <c r="F56" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>86</v>
+      </c>
+      <c r="D57" t="s">
+        <v>49</v>
+      </c>
+      <c r="F57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58">
         <v>-22.96</v>
       </c>
-      <c r="C56">
+      <c r="C58">
         <v>-40.72</v>
       </c>
-      <c r="D56" t="s">
-        <v>27</v>
-      </c>
-      <c r="F56" t="s">
-        <v>34</v>
-      </c>
-      <c r="G56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>91</v>
-      </c>
-      <c r="B57">
+      <c r="D58" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>88</v>
+      </c>
+      <c r="B59">
         <v>-22.13</v>
       </c>
-      <c r="C57">
+      <c r="C59">
         <v>-39.96</v>
       </c>
-      <c r="D57" t="s">
-        <v>31</v>
-      </c>
-      <c r="F57" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D58" t="s">
-        <v>83</v>
-      </c>
-      <c r="F58" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>93</v>
+      <c r="D59" t="s">
+        <v>28</v>
       </c>
       <c r="F59" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>94</v>
-      </c>
-      <c r="B60">
-        <v>-22.55</v>
-      </c>
-      <c r="C60">
-        <v>-40.25</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="D60" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="F60" t="s">
-        <v>34</v>
-      </c>
-      <c r="G60" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>95</v>
-      </c>
-      <c r="B61">
-        <v>-22.34</v>
-      </c>
-      <c r="C61">
-        <v>-40.19</v>
-      </c>
-      <c r="D61" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="F61" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B62">
-        <v>-22.66</v>
+        <v>-22.55</v>
       </c>
       <c r="C62">
-        <v>-40.229999999999997</v>
+        <v>-40.25</v>
       </c>
       <c r="D62" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F62" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G62" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>98</v>
+        <v>92</v>
+      </c>
+      <c r="B63">
+        <v>-22.34</v>
+      </c>
+      <c r="C63">
+        <v>-40.19</v>
       </c>
       <c r="D63" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="F63" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>93</v>
+      </c>
+      <c r="B64">
+        <v>-22.66</v>
+      </c>
+      <c r="C64">
+        <v>-40.229999999999997</v>
       </c>
       <c r="D64" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="F64" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="G64" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>100</v>
-      </c>
-      <c r="B65">
+        <v>95</v>
+      </c>
+      <c r="D65" t="s">
+        <v>80</v>
+      </c>
+      <c r="F65" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" t="s">
+        <v>80</v>
+      </c>
+      <c r="F66" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>97</v>
+      </c>
+      <c r="B67">
         <v>-22.42</v>
       </c>
-      <c r="C65">
+      <c r="C67">
         <v>-39.950000000000003</v>
       </c>
-      <c r="D65" t="s">
-        <v>31</v>
-      </c>
-      <c r="F65" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B66">
-        <v>-21.96</v>
-      </c>
-      <c r="C66">
-        <v>-39.82</v>
-      </c>
-      <c r="D66" t="s">
-        <v>31</v>
-      </c>
-      <c r="F66" t="s">
-        <v>34</v>
-      </c>
-      <c r="G66" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B67">
-        <v>-21.99</v>
-      </c>
-      <c r="C67">
-        <v>-39.729999999999997</v>
-      </c>
       <c r="D67" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="F67" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B68">
-        <v>-22.62</v>
+        <v>-21.96</v>
       </c>
       <c r="C68">
-        <v>-39.979999999999997</v>
+        <v>-39.82</v>
       </c>
       <c r="D68" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="F68" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G68" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B69">
-        <v>-21.23</v>
+        <v>-21.99</v>
       </c>
       <c r="C69">
-        <v>-40.04</v>
+        <v>-39.729999999999997</v>
       </c>
       <c r="D69" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="F69" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="B70">
-        <v>-25.022000999999999</v>
+        <v>-22.62</v>
       </c>
       <c r="C70">
-        <v>-42.667259000000001</v>
+        <v>-39.979999999999997</v>
       </c>
       <c r="D70" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="F70" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="G70" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B71">
-        <v>-25.656942000000001</v>
+        <v>-21.23</v>
       </c>
       <c r="C71">
-        <v>-42.858749000000003</v>
+        <v>-40.04</v>
       </c>
       <c r="D71" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F71" t="s">
-        <v>108</v>
-      </c>
-      <c r="G71" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="B72">
-        <v>-24.776168999999999</v>
+        <v>-25.022000999999999</v>
       </c>
       <c r="C72">
-        <v>-42.720005</v>
+        <v>-42.667259000000001</v>
       </c>
       <c r="D72" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F72" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G72" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B73">
-        <v>-24.64</v>
+        <v>-25.656942000000001</v>
       </c>
       <c r="C73">
-        <v>-42.51</v>
+        <v>-42.858749000000003</v>
       </c>
       <c r="D73" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F73" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G73" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B74">
-        <v>-24.78</v>
+        <v>-24.776168999999999</v>
       </c>
       <c r="C74">
-        <v>-42.5</v>
+        <v>-42.720005</v>
       </c>
       <c r="D74" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F74" t="s">
+        <v>105</v>
+      </c>
+      <c r="G74" t="s">
         <v>108</v>
-      </c>
-      <c r="G74" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B75">
-        <v>-24.68</v>
+        <v>-24.64</v>
       </c>
       <c r="C75">
-        <v>-42.5</v>
+        <v>-42.51</v>
       </c>
       <c r="D75" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F75" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G75" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B76">
-        <v>-24.63</v>
+        <v>-24.78</v>
       </c>
       <c r="C76">
-        <v>-42.41</v>
+        <v>-42.5</v>
       </c>
       <c r="D76" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F76" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G76" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B77">
-        <v>-24.67</v>
+        <v>-24.68</v>
       </c>
       <c r="C77">
-        <v>-42.38</v>
+        <v>-42.5</v>
       </c>
       <c r="D77" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F77" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G77" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B78">
-        <v>-24.54</v>
+        <v>-24.63</v>
       </c>
       <c r="C78">
-        <v>-42.46</v>
+        <v>-42.41</v>
       </c>
       <c r="D78" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F78" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G78" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B79">
-        <v>-24.59</v>
+        <v>-24.67</v>
       </c>
       <c r="C79">
-        <v>-42.56</v>
+        <v>-42.38</v>
       </c>
       <c r="D79" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F79" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G79" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B80">
-        <v>-24.74</v>
+        <v>-24.54</v>
       </c>
       <c r="C80">
-        <v>-42.51</v>
+        <v>-42.46</v>
       </c>
       <c r="D80" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F80" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G80" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B81">
-        <v>-25.798373999999999</v>
+        <v>-24.59</v>
       </c>
       <c r="C81">
-        <v>-43.262680000000003</v>
+        <v>-42.56</v>
       </c>
       <c r="D81" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F81" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G81" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B82">
-        <v>-25.671883000000001</v>
+        <v>-24.74</v>
       </c>
       <c r="C82">
-        <v>-43.205939999999998</v>
+        <v>-42.51</v>
       </c>
       <c r="D82" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F82" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G82" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="B83">
-        <v>-25.226118</v>
+        <v>-25.798373999999999</v>
       </c>
       <c r="C83">
-        <v>-42.56982</v>
+        <v>-43.262680000000003</v>
       </c>
       <c r="D83" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F83" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G83" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B84">
-        <v>-24.685623</v>
+        <v>-25.671883000000001</v>
       </c>
       <c r="C84">
-        <v>-42.293922000000002</v>
+        <v>-43.205939999999998</v>
       </c>
       <c r="D84" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F84" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G84" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B85">
-        <v>-22.1</v>
+        <v>-25.226118</v>
       </c>
       <c r="C85">
-        <v>-39.909999999999997</v>
+        <v>-42.56982</v>
       </c>
       <c r="D85" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="F85" t="s">
-        <v>34</v>
+        <v>105</v>
+      </c>
+      <c r="G85" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B86">
-        <v>-23.08</v>
+        <v>-24.685623</v>
       </c>
       <c r="C86">
-        <v>-40.99</v>
+        <v>-42.293922000000002</v>
       </c>
       <c r="D86" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="G86" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
+      </c>
+      <c r="B87">
+        <v>-22.1</v>
+      </c>
+      <c r="C87">
+        <v>-39.909999999999997</v>
       </c>
       <c r="D87" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="F87" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
+      </c>
+      <c r="B88">
+        <v>-23.08</v>
+      </c>
+      <c r="C88">
+        <v>-40.99</v>
+      </c>
+      <c r="D88" t="s">
+        <v>49</v>
       </c>
       <c r="F88" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="G88" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B89">
-        <v>-22.14</v>
-      </c>
-      <c r="C89">
-        <v>-39.92</v>
+        <v>126</v>
       </c>
       <c r="D89" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="F89" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B90">
-        <v>-22.14</v>
-      </c>
-      <c r="C90">
-        <v>-39.92</v>
-      </c>
-      <c r="D90" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="F90" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B91">
-        <v>-23.3827</v>
+        <v>-22.14</v>
       </c>
       <c r="C91">
-        <v>-40.073999999999998</v>
+        <v>-39.92</v>
       </c>
       <c r="D91" t="s">
-        <v>27</v>
-      </c>
-      <c r="E91" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="F91" t="s">
-        <v>108</v>
-      </c>
-      <c r="G91" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>137</v>
+        <v>130</v>
+      </c>
+      <c r="B92">
+        <v>-22.14</v>
+      </c>
+      <c r="C92">
+        <v>-39.92</v>
       </c>
       <c r="D92" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F92" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B93">
+        <v>-23.3827</v>
+      </c>
+      <c r="C93">
+        <v>-40.073999999999998</v>
+      </c>
+      <c r="D93" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93" t="s">
+        <v>132</v>
+      </c>
+      <c r="F93" t="s">
+        <v>105</v>
+      </c>
+      <c r="G93" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F95" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F96" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>137</v>
+      </c>
+      <c r="B97">
+        <v>-21.33</v>
+      </c>
+      <c r="C97">
+        <v>-40.049999999999997</v>
+      </c>
+      <c r="D97" t="s">
+        <v>28</v>
+      </c>
+      <c r="E97" t="s">
         <v>138</v>
       </c>
-      <c r="F93" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="5" t="s">
+      <c r="F97" t="s">
         <v>139</v>
-      </c>
-      <c r="F94" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>140</v>
-      </c>
-      <c r="B95">
-        <v>-21.33</v>
-      </c>
-      <c r="C95">
-        <v>-40.049999999999997</v>
-      </c>
-      <c r="D95" t="s">
-        <v>31</v>
-      </c>
-      <c r="E95" t="s">
-        <v>141</v>
-      </c>
-      <c r="F95" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD5CD0DA-EE9D-4258-93A6-1A755C80F899}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4F27AD-19AD-466E-A93F-63BBDA06DB2A}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$1</definedName>
@@ -2553,4 +2554,13 @@
   <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A458B0-5351-487A-ABCF-BB5088AD3353}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4F27AD-19AD-466E-A93F-63BBDA06DB2A}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25C844CB-BE17-4B48-9611-7D619657EC00}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="149">
   <si>
     <t>unidade</t>
   </si>
@@ -475,6 +475,15 @@
   </si>
   <si>
     <t>Fundeio - RIO</t>
+  </si>
+  <si>
+    <t>albacora</t>
+  </si>
+  <si>
+    <t>viola</t>
+  </si>
+  <si>
+    <t>pargo</t>
   </si>
 </sst>
 </file>
@@ -1616,6 +1625,9 @@
       <c r="F40" t="s">
         <v>31</v>
       </c>
+      <c r="G40" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -1900,6 +1912,9 @@
       <c r="F59" t="s">
         <v>31</v>
       </c>
+      <c r="G59" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="60" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
@@ -1955,6 +1970,9 @@
       </c>
       <c r="F63" t="s">
         <v>31</v>
+      </c>
+      <c r="G63" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">

--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25C844CB-BE17-4B48-9611-7D619657EC00}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EC80038-80E2-4C65-8FDD-A34ABE1C0941}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="156">
   <si>
     <t>unidade</t>
   </si>
@@ -366,33 +366,12 @@
     <t>itapu</t>
   </si>
   <si>
-    <t>P-74</t>
-  </si>
-  <si>
     <t>buzios</t>
   </si>
   <si>
-    <t>p-75_FSO</t>
-  </si>
-  <si>
-    <t>p-76</t>
-  </si>
-  <si>
-    <t>p-77_FSO</t>
-  </si>
-  <si>
-    <t>p-78</t>
-  </si>
-  <si>
-    <t>p-79</t>
-  </si>
-  <si>
     <t>almirante barroso_FSO</t>
   </si>
   <si>
-    <t>almirante tamandaré</t>
-  </si>
-  <si>
     <t>CIDADE SÃO PAULO</t>
   </si>
   <si>
@@ -484,6 +463,48 @@
   </si>
   <si>
     <t>pargo</t>
+  </si>
+  <si>
+    <t>jubarte</t>
+  </si>
+  <si>
+    <t>baleia anã</t>
+  </si>
+  <si>
+    <t>P-75_FSO</t>
+  </si>
+  <si>
+    <t>P-76</t>
+  </si>
+  <si>
+    <t>P-77_FSO</t>
+  </si>
+  <si>
+    <t>P-78</t>
+  </si>
+  <si>
+    <t>P-79</t>
+  </si>
+  <si>
+    <t>ALMIRANTE TAMANDARÉ</t>
+  </si>
+  <si>
+    <t>PETROBRAS 74 (P-74)</t>
+  </si>
+  <si>
+    <t>PNA-1</t>
+  </si>
+  <si>
+    <t>Fixa</t>
+  </si>
+  <si>
+    <t>namorado</t>
+  </si>
+  <si>
+    <t>PGP-1</t>
+  </si>
+  <si>
+    <t>garoupa</t>
   </si>
 </sst>
 </file>
@@ -899,13 +920,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.88671875" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" customWidth="1"/>
     <col min="5" max="5" width="15.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1065,7 +1086,7 @@
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1082,7 +1103,7 @@
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1099,7 +1120,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1209,6 +1230,9 @@
       <c r="F17" t="s">
         <v>31</v>
       </c>
+      <c r="G17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
@@ -1304,6 +1328,12 @@
       <c r="D22" t="s">
         <v>28</v>
       </c>
+      <c r="F22" t="s">
+        <v>103</v>
+      </c>
+      <c r="G22" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
@@ -1395,6 +1425,9 @@
       <c r="F27" t="s">
         <v>31</v>
       </c>
+      <c r="G27" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
@@ -1434,6 +1467,9 @@
       <c r="F30" t="s">
         <v>31</v>
       </c>
+      <c r="G30" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1449,7 +1485,10 @@
         <v>24</v>
       </c>
       <c r="F31" t="s">
-        <v>31</v>
+        <v>103</v>
+      </c>
+      <c r="G31" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1626,7 +1665,7 @@
         <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -1697,7 +1736,10 @@
         <v>24</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>103</v>
+      </c>
+      <c r="G44" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -1727,6 +1769,9 @@
       <c r="F46" t="s">
         <v>31</v>
       </c>
+      <c r="G46" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -1913,7 +1958,7 @@
         <v>31</v>
       </c>
       <c r="G59" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1952,7 +1997,7 @@
         <v>31</v>
       </c>
       <c r="G62" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -1972,7 +2017,7 @@
         <v>31</v>
       </c>
       <c r="G63" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -2107,10 +2152,13 @@
       <c r="F71" t="s">
         <v>103</v>
       </c>
+      <c r="G71" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B72">
         <v>-25.022000999999999</v>
@@ -2125,7 +2173,7 @@
         <v>105</v>
       </c>
       <c r="G72" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -2170,7 +2218,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="B75">
         <v>-24.64</v>
@@ -2185,12 +2233,12 @@
         <v>105</v>
       </c>
       <c r="G75" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="B76">
         <v>-24.78</v>
@@ -2205,12 +2253,12 @@
         <v>105</v>
       </c>
       <c r="G76" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="B77">
         <v>-24.68</v>
@@ -2225,12 +2273,12 @@
         <v>105</v>
       </c>
       <c r="G77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="B78">
         <v>-24.63</v>
@@ -2245,12 +2293,12 @@
         <v>105</v>
       </c>
       <c r="G78" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="B79">
         <v>-24.67</v>
@@ -2265,12 +2313,12 @@
         <v>105</v>
       </c>
       <c r="G79" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="B80">
         <v>-24.54</v>
@@ -2285,12 +2333,12 @@
         <v>105</v>
       </c>
       <c r="G80" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B81">
         <v>-24.59</v>
@@ -2305,12 +2353,12 @@
         <v>105</v>
       </c>
       <c r="G81" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="B82">
         <v>-24.74</v>
@@ -2325,12 +2373,12 @@
         <v>105</v>
       </c>
       <c r="G82" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B83">
         <v>-25.798373999999999</v>
@@ -2345,12 +2393,12 @@
         <v>105</v>
       </c>
       <c r="G83" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B84">
         <v>-25.671883000000001</v>
@@ -2365,12 +2413,12 @@
         <v>105</v>
       </c>
       <c r="G84" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B85">
         <v>-25.226118</v>
@@ -2385,12 +2433,12 @@
         <v>105</v>
       </c>
       <c r="G85" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B86">
         <v>-24.685623</v>
@@ -2405,12 +2453,12 @@
         <v>105</v>
       </c>
       <c r="G86" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B87">
         <v>-22.1</v>
@@ -2427,7 +2475,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B88">
         <v>-23.08</v>
@@ -2442,15 +2490,15 @@
         <v>31</v>
       </c>
       <c r="G88" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D89" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F89" t="s">
         <v>31</v>
@@ -2458,7 +2506,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F90" t="s">
         <v>31</v>
@@ -2466,7 +2514,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B91">
         <v>-22.14</v>
@@ -2483,7 +2531,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B92">
         <v>-22.14</v>
@@ -2500,7 +2548,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B93">
         <v>-23.3827</v>
@@ -2512,18 +2560,18 @@
         <v>24</v>
       </c>
       <c r="E93" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F93" t="s">
         <v>105</v>
       </c>
       <c r="G93" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D94" t="s">
         <v>24</v>
@@ -2534,7 +2582,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F95" t="s">
         <v>31</v>
@@ -2542,15 +2590,15 @@
     </row>
     <row r="96" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="F96" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B97">
         <v>-21.33</v>
@@ -2562,10 +2610,53 @@
         <v>28</v>
       </c>
       <c r="E97" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F97" t="s">
-        <v>139</v>
+        <v>132</v>
+      </c>
+      <c r="G97" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B98">
+        <v>-22.436900000000001</v>
+      </c>
+      <c r="C98">
+        <v>-40.425800000000002</v>
+      </c>
+      <c r="D98" t="s">
+        <v>152</v>
+      </c>
+      <c r="F98" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B99">
+        <v>-22.374779</v>
+      </c>
+      <c r="C99">
+        <v>-40.417454999999997</v>
+      </c>
+      <c r="D99" t="s">
+        <v>152</v>
+      </c>
+      <c r="F99" t="s">
+        <v>31</v>
+      </c>
+      <c r="G99" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EC80038-80E2-4C65-8FDD-A34ABE1C0941}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCA6BBB1-D3EA-4EEF-8B93-CD64A72C7CC2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$99</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="155">
   <si>
     <t>unidade</t>
   </si>
@@ -493,9 +493,6 @@
   </si>
   <si>
     <t>PNA-1</t>
-  </si>
-  <si>
-    <t>Fixa</t>
   </si>
   <si>
     <t>namorado</t>
@@ -920,6 +917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -953,7 +951,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -970,7 +968,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -987,7 +985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1004,7 +1002,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1021,7 +1019,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1038,7 +1036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1055,7 +1053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1072,7 +1070,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -1089,7 +1087,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -1106,7 +1104,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1123,7 +1121,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -1140,7 +1138,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1157,7 +1155,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1174,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1194,7 +1192,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
@@ -1214,7 +1212,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>30</v>
       </c>
@@ -1234,7 +1232,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -1252,7 +1250,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>33</v>
       </c>
@@ -1269,7 +1267,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1292,7 +1290,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
@@ -1315,7 +1313,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>39</v>
       </c>
@@ -1335,7 +1333,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>40</v>
       </c>
@@ -1349,7 +1347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -1372,7 +1370,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -1392,7 +1390,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1409,7 +1407,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -1451,7 +1449,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -1471,7 +1469,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -1502,7 +1500,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -1519,7 +1517,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -1539,7 +1537,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -1559,7 +1557,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -1582,7 +1580,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -1605,7 +1603,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -1625,7 +1623,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>65</v>
       </c>
@@ -1648,7 +1646,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>67</v>
       </c>
@@ -1668,7 +1666,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -1691,7 +1689,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -1722,7 +1720,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -1742,7 +1740,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -1753,7 +1751,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -1773,7 +1771,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -1796,7 +1794,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -1807,7 +1805,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -1818,7 +1816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -1835,7 +1833,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -1846,7 +1844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>81</v>
       </c>
@@ -1921,7 +1919,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -1941,7 +1939,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>88</v>
       </c>
@@ -1961,7 +1959,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>89</v>
       </c>
@@ -1972,7 +1970,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>90</v>
       </c>
@@ -1980,7 +1978,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>91</v>
       </c>
@@ -2000,7 +1998,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>92</v>
       </c>
@@ -2020,7 +2018,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>93</v>
       </c>
@@ -2040,7 +2038,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>95</v>
       </c>
@@ -2051,7 +2049,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>96</v>
       </c>
@@ -2062,7 +2060,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>97</v>
       </c>
@@ -2079,7 +2077,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>98</v>
       </c>
@@ -2099,7 +2097,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>99</v>
       </c>
@@ -2116,7 +2114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>100</v>
       </c>
@@ -2136,7 +2134,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>102</v>
       </c>
@@ -2156,7 +2154,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>135</v>
       </c>
@@ -2176,7 +2174,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>104</v>
       </c>
@@ -2196,7 +2194,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>107</v>
       </c>
@@ -2216,7 +2214,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>150</v>
       </c>
@@ -2236,7 +2234,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>144</v>
       </c>
@@ -2256,7 +2254,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>145</v>
       </c>
@@ -2276,7 +2274,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>146</v>
       </c>
@@ -2296,7 +2294,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>147</v>
       </c>
@@ -2316,7 +2314,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>148</v>
       </c>
@@ -2336,7 +2334,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>110</v>
       </c>
@@ -2356,7 +2354,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>149</v>
       </c>
@@ -2376,7 +2374,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>111</v>
       </c>
@@ -2396,7 +2394,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>113</v>
       </c>
@@ -2416,7 +2414,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>133</v>
       </c>
@@ -2436,7 +2434,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>114</v>
       </c>
@@ -2456,7 +2454,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>116</v>
       </c>
@@ -2493,7 +2491,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>119</v>
       </c>
@@ -2504,7 +2502,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>121</v>
       </c>
@@ -2512,7 +2510,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>122</v>
       </c>
@@ -2529,7 +2527,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>123</v>
       </c>
@@ -2546,7 +2544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>124</v>
       </c>
@@ -2569,7 +2567,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>127</v>
       </c>
@@ -2580,7 +2578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>128</v>
       </c>
@@ -2588,7 +2586,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>129</v>
       </c>
@@ -2596,7 +2594,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>130</v>
       </c>
@@ -2630,18 +2628,18 @@
         <v>-40.425800000000002</v>
       </c>
       <c r="D98" t="s">
+        <v>49</v>
+      </c>
+      <c r="F98" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98" t="s">
         <v>152</v>
-      </c>
-      <c r="F98" t="s">
-        <v>31</v>
-      </c>
-      <c r="G98" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B99">
         <v>-22.374779</v>
@@ -2650,17 +2648,24 @@
         <v>-40.417454999999997</v>
       </c>
       <c r="D99" t="s">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="F99" t="s">
         <v>31</v>
       </c>
       <c r="G99" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G99" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Fixa"/>
+        <filter val="Fixa (Habitada)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCA6BBB1-D3EA-4EEF-8B93-CD64A72C7CC2}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B43F0510-586C-4623-AE14-1765C52AD85C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="158">
   <si>
     <t>unidade</t>
   </si>
@@ -502,6 +502,15 @@
   </si>
   <si>
     <t>garoupa</t>
+  </si>
+  <si>
+    <t>PETROBRAS 65 (P-65)</t>
+  </si>
+  <si>
+    <t>marimbá</t>
+  </si>
+  <si>
+    <t>PETROBRAS 08 (P-08)</t>
   </si>
 </sst>
 </file>
@@ -917,8 +926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.88671875" customWidth="1"/>
@@ -951,7 +959,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -968,7 +976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -985,7 +993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1002,7 +1010,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1019,7 +1027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1036,7 +1044,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1053,7 +1061,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1070,7 +1078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -1087,7 +1095,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -1104,7 +1112,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1121,7 +1129,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -1138,7 +1146,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1155,7 +1163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1172,7 +1180,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1192,7 +1200,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
@@ -1212,7 +1220,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>30</v>
       </c>
@@ -1232,7 +1240,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -1250,7 +1258,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>33</v>
       </c>
@@ -1267,7 +1275,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1290,7 +1298,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
@@ -1313,7 +1321,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>39</v>
       </c>
@@ -1333,7 +1341,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>40</v>
       </c>
@@ -1347,7 +1355,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -1370,7 +1378,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -1390,7 +1398,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1407,7 +1415,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -1449,7 +1457,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -1469,7 +1477,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -1500,7 +1508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -1517,7 +1525,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -1537,7 +1545,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -1557,7 +1565,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -1580,7 +1588,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -1603,7 +1611,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -1623,7 +1631,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>65</v>
       </c>
@@ -1646,7 +1654,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>67</v>
       </c>
@@ -1666,7 +1674,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -1689,7 +1697,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -1720,7 +1728,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -1740,7 +1748,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -1751,7 +1759,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -1771,7 +1779,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -1794,7 +1802,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -1805,7 +1813,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -1816,7 +1824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -1833,7 +1841,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -1844,7 +1852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>81</v>
       </c>
@@ -1919,7 +1927,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -1939,119 +1947,128 @@
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59">
+        <v>-22.672789000000002</v>
+      </c>
+      <c r="C59">
+        <v>-40.546345000000002</v>
+      </c>
+      <c r="D59" t="s">
+        <v>80</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>88</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>-22.13</v>
       </c>
-      <c r="C59">
+      <c r="C60">
         <v>-39.96</v>
       </c>
-      <c r="D59" t="s">
-        <v>28</v>
-      </c>
-      <c r="F59" t="s">
-        <v>31</v>
-      </c>
-      <c r="G59" t="s">
+      <c r="D60" t="s">
+        <v>28</v>
+      </c>
+      <c r="F60" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="4" t="s">
+    <row r="61" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D61" t="s">
         <v>80</v>
       </c>
-      <c r="F60" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="F61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>90</v>
       </c>
-      <c r="F61" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="F62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>91</v>
       </c>
-      <c r="B62">
+      <c r="B63">
         <v>-22.55</v>
       </c>
-      <c r="C62">
+      <c r="C63">
         <v>-40.25</v>
       </c>
-      <c r="D62" t="s">
-        <v>28</v>
-      </c>
-      <c r="F62" t="s">
-        <v>31</v>
-      </c>
-      <c r="G62" t="s">
+      <c r="D63" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>92</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <v>-22.34</v>
       </c>
-      <c r="C63">
+      <c r="C64">
         <v>-40.19</v>
       </c>
-      <c r="D63" t="s">
-        <v>28</v>
-      </c>
-      <c r="F63" t="s">
-        <v>31</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="D64" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" t="s">
+        <v>31</v>
+      </c>
+      <c r="G64" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>93</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <v>-22.66</v>
       </c>
-      <c r="C64">
+      <c r="C65">
         <v>-40.229999999999997</v>
       </c>
-      <c r="D64" t="s">
-        <v>28</v>
-      </c>
-      <c r="F64" t="s">
-        <v>31</v>
-      </c>
-      <c r="G64" t="s">
+      <c r="D65" t="s">
+        <v>28</v>
+      </c>
+      <c r="F65" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>95</v>
-      </c>
-      <c r="D65" t="s">
-        <v>80</v>
-      </c>
-      <c r="F65" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>96</v>
       </c>
       <c r="D66" t="s">
         <v>80</v>
@@ -2060,69 +2077,63 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>96</v>
+      </c>
+      <c r="D67" t="s">
+        <v>80</v>
+      </c>
+      <c r="F67" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>97</v>
       </c>
-      <c r="B67">
+      <c r="B68">
         <v>-22.42</v>
       </c>
-      <c r="C67">
+      <c r="C68">
         <v>-39.950000000000003</v>
       </c>
-      <c r="D67" t="s">
-        <v>28</v>
-      </c>
-      <c r="F67" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="s">
+      <c r="D68" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B68">
+      <c r="B69">
         <v>-21.96</v>
       </c>
-      <c r="C68">
+      <c r="C69">
         <v>-39.82</v>
       </c>
-      <c r="D68" t="s">
-        <v>28</v>
-      </c>
-      <c r="F68" t="s">
-        <v>31</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="D69" t="s">
+        <v>28</v>
+      </c>
+      <c r="F69" t="s">
+        <v>31</v>
+      </c>
+      <c r="G69" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="5" t="s">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B69">
+      <c r="B70">
         <v>-21.99</v>
       </c>
-      <c r="C69">
+      <c r="C70">
         <v>-39.729999999999997</v>
-      </c>
-      <c r="D69" t="s">
-        <v>80</v>
-      </c>
-      <c r="F69" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B70">
-        <v>-22.62</v>
-      </c>
-      <c r="C70">
-        <v>-39.979999999999997</v>
       </c>
       <c r="D70" t="s">
         <v>80</v>
@@ -2130,79 +2141,76 @@
       <c r="F70" t="s">
         <v>31</v>
       </c>
-      <c r="G70" t="s">
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71">
+        <v>-22.62</v>
+      </c>
+      <c r="C71">
+        <v>-39.979999999999997</v>
+      </c>
+      <c r="D71" t="s">
+        <v>80</v>
+      </c>
+      <c r="F71" t="s">
+        <v>31</v>
+      </c>
+      <c r="G71" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B71">
+      <c r="B72">
         <v>-21.23</v>
       </c>
-      <c r="C71">
+      <c r="C72">
         <v>-40.04</v>
       </c>
-      <c r="D71" t="s">
-        <v>28</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="D72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72" t="s">
         <v>103</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G72" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="s">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73">
+        <v>-22.701767</v>
+      </c>
+      <c r="C73">
+        <v>-40.677059</v>
+      </c>
+      <c r="D73" t="s">
+        <v>80</v>
+      </c>
+      <c r="F73" t="s">
+        <v>31</v>
+      </c>
+      <c r="G73" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B72">
+      <c r="B74">
         <v>-25.022000999999999</v>
       </c>
-      <c r="C72">
+      <c r="C74">
         <v>-42.667259000000001</v>
-      </c>
-      <c r="D72" t="s">
-        <v>28</v>
-      </c>
-      <c r="F72" t="s">
-        <v>105</v>
-      </c>
-      <c r="G72" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B73">
-        <v>-25.656942000000001</v>
-      </c>
-      <c r="C73">
-        <v>-42.858749000000003</v>
-      </c>
-      <c r="D73" t="s">
-        <v>28</v>
-      </c>
-      <c r="F73" t="s">
-        <v>105</v>
-      </c>
-      <c r="G73" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B74">
-        <v>-24.776168999999999</v>
-      </c>
-      <c r="C74">
-        <v>-42.720005</v>
       </c>
       <c r="D74" t="s">
         <v>28</v>
@@ -2211,18 +2219,18 @@
         <v>105</v>
       </c>
       <c r="G74" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="B75">
-        <v>-24.64</v>
+        <v>-25.656942000000001</v>
       </c>
       <c r="C75">
-        <v>-42.51</v>
+        <v>-42.858749000000003</v>
       </c>
       <c r="D75" t="s">
         <v>28</v>
@@ -2231,18 +2239,18 @@
         <v>105</v>
       </c>
       <c r="G75" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="B76">
-        <v>-24.78</v>
+        <v>-24.776168999999999</v>
       </c>
       <c r="C76">
-        <v>-42.5</v>
+        <v>-42.720005</v>
       </c>
       <c r="D76" t="s">
         <v>28</v>
@@ -2251,18 +2259,18 @@
         <v>105</v>
       </c>
       <c r="G76" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B77">
-        <v>-24.68</v>
+        <v>-24.64</v>
       </c>
       <c r="C77">
-        <v>-42.5</v>
+        <v>-42.51</v>
       </c>
       <c r="D77" t="s">
         <v>28</v>
@@ -2274,15 +2282,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B78">
-        <v>-24.63</v>
+        <v>-24.78</v>
       </c>
       <c r="C78">
-        <v>-42.41</v>
+        <v>-42.5</v>
       </c>
       <c r="D78" t="s">
         <v>28</v>
@@ -2294,15 +2302,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B79">
-        <v>-24.67</v>
+        <v>-24.68</v>
       </c>
       <c r="C79">
-        <v>-42.38</v>
+        <v>-42.5</v>
       </c>
       <c r="D79" t="s">
         <v>28</v>
@@ -2314,15 +2322,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B80">
-        <v>-24.54</v>
+        <v>-24.63</v>
       </c>
       <c r="C80">
-        <v>-42.46</v>
+        <v>-42.41</v>
       </c>
       <c r="D80" t="s">
         <v>28</v>
@@ -2334,15 +2342,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="B81">
-        <v>-24.59</v>
+        <v>-24.67</v>
       </c>
       <c r="C81">
-        <v>-42.56</v>
+        <v>-42.38</v>
       </c>
       <c r="D81" t="s">
         <v>28</v>
@@ -2354,15 +2362,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B82">
-        <v>-24.74</v>
+        <v>-24.54</v>
       </c>
       <c r="C82">
-        <v>-42.51</v>
+        <v>-42.46</v>
       </c>
       <c r="D82" t="s">
         <v>28</v>
@@ -2374,15 +2382,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B83">
-        <v>-25.798373999999999</v>
+        <v>-24.59</v>
       </c>
       <c r="C83">
-        <v>-43.262680000000003</v>
+        <v>-42.56</v>
       </c>
       <c r="D83" t="s">
         <v>28</v>
@@ -2391,18 +2399,18 @@
         <v>105</v>
       </c>
       <c r="G83" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="B84">
-        <v>-25.671883000000001</v>
+        <v>-24.74</v>
       </c>
       <c r="C84">
-        <v>-43.205939999999998</v>
+        <v>-42.51</v>
       </c>
       <c r="D84" t="s">
         <v>28</v>
@@ -2411,18 +2419,18 @@
         <v>105</v>
       </c>
       <c r="G84" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="B85">
-        <v>-25.226118</v>
+        <v>-25.798373999999999</v>
       </c>
       <c r="C85">
-        <v>-42.56982</v>
+        <v>-43.262680000000003</v>
       </c>
       <c r="D85" t="s">
         <v>28</v>
@@ -2431,18 +2439,18 @@
         <v>105</v>
       </c>
       <c r="G85" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B86">
-        <v>-24.685623</v>
+        <v>-25.671883000000001</v>
       </c>
       <c r="C86">
-        <v>-42.293922000000002</v>
+        <v>-43.205939999999998</v>
       </c>
       <c r="D86" t="s">
         <v>28</v>
@@ -2451,125 +2459,131 @@
         <v>105</v>
       </c>
       <c r="G86" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B87">
-        <v>-22.1</v>
+        <v>-25.226118</v>
       </c>
       <c r="C87">
-        <v>-39.909999999999997</v>
+        <v>-42.56982</v>
       </c>
       <c r="D87" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F87" t="s">
-        <v>31</v>
+        <v>105</v>
+      </c>
+      <c r="G87" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B88">
+        <v>-24.685623</v>
+      </c>
+      <c r="C88">
+        <v>-42.293922000000002</v>
+      </c>
+      <c r="D88" t="s">
+        <v>28</v>
+      </c>
+      <c r="F88" t="s">
+        <v>105</v>
+      </c>
+      <c r="G88" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B89">
+        <v>-22.1</v>
+      </c>
+      <c r="C89">
+        <v>-39.909999999999997</v>
+      </c>
+      <c r="D89" t="s">
+        <v>80</v>
+      </c>
+      <c r="F89" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B88">
+      <c r="B90">
         <v>-23.08</v>
       </c>
-      <c r="C88">
+      <c r="C90">
         <v>-40.99</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D90" t="s">
         <v>49</v>
       </c>
-      <c r="F88" t="s">
-        <v>31</v>
-      </c>
-      <c r="G88" t="s">
+      <c r="F90" t="s">
+        <v>31</v>
+      </c>
+      <c r="G90" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="5" t="s">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D91" t="s">
         <v>120</v>
       </c>
-      <c r="F89" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
+      <c r="F91" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F90" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
+      <c r="F92" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B91">
+      <c r="B93">
         <v>-22.14</v>
       </c>
-      <c r="C91">
+      <c r="C93">
         <v>-39.92</v>
-      </c>
-      <c r="D91" t="s">
-        <v>24</v>
-      </c>
-      <c r="F91" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B92">
-        <v>-22.14</v>
-      </c>
-      <c r="C92">
-        <v>-39.92</v>
-      </c>
-      <c r="D92" t="s">
-        <v>24</v>
-      </c>
-      <c r="F92" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B93">
-        <v>-23.3827</v>
-      </c>
-      <c r="C93">
-        <v>-40.073999999999998</v>
       </c>
       <c r="D93" t="s">
         <v>24</v>
       </c>
-      <c r="E93" t="s">
-        <v>125</v>
-      </c>
       <c r="F93" t="s">
-        <v>105</v>
-      </c>
-      <c r="G93" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
+      </c>
+      <c r="B94">
+        <v>-22.14</v>
+      </c>
+      <c r="C94">
+        <v>-39.92</v>
       </c>
       <c r="D94" t="s">
         <v>24</v>
@@ -2578,94 +2592,121 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B95">
+        <v>-23.3827</v>
+      </c>
+      <c r="C95">
+        <v>-40.073999999999998</v>
+      </c>
+      <c r="D95" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" t="s">
+        <v>125</v>
+      </c>
+      <c r="F95" t="s">
+        <v>105</v>
+      </c>
+      <c r="G95" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D96" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F95" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
+      <c r="F97" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F96" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="F98" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>130</v>
       </c>
-      <c r="B97">
+      <c r="B99">
         <v>-21.33</v>
       </c>
-      <c r="C97">
+      <c r="C99">
         <v>-40.049999999999997</v>
       </c>
-      <c r="D97" t="s">
-        <v>28</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="D99" t="s">
+        <v>28</v>
+      </c>
+      <c r="E99" t="s">
         <v>131</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F99" t="s">
         <v>132</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G99" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="s">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B98">
+      <c r="B100">
         <v>-22.436900000000001</v>
       </c>
-      <c r="C98">
+      <c r="C100">
         <v>-40.425800000000002</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D100" t="s">
         <v>49</v>
       </c>
-      <c r="F98" t="s">
-        <v>31</v>
-      </c>
-      <c r="G98" t="s">
+      <c r="F100" t="s">
+        <v>31</v>
+      </c>
+      <c r="G100" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B99">
+      <c r="B101">
         <v>-22.374779</v>
       </c>
-      <c r="C99">
+      <c r="C101">
         <v>-40.417454999999997</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D101" t="s">
         <v>49</v>
       </c>
-      <c r="F99" t="s">
-        <v>31</v>
-      </c>
-      <c r="G99" t="s">
+      <c r="F101" t="s">
+        <v>31</v>
+      </c>
+      <c r="G101" t="s">
         <v>154</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G99" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Fixa"/>
-        <filter val="Fixa (Habitada)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G101" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B43F0510-586C-4623-AE14-1765C52AD85C}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{706D6B2C-5D46-4427-8384-F3B56F7E30D9}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$102</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="160">
   <si>
     <t>unidade</t>
   </si>
@@ -511,6 +511,12 @@
   </si>
   <si>
     <t>PETROBRAS 08 (P-08)</t>
+  </si>
+  <si>
+    <t>FPSO CIDADE CARAGUATATUBA</t>
+  </si>
+  <si>
+    <t>lapa</t>
   </si>
 </sst>
 </file>
@@ -926,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.88671875" customWidth="1"/>
@@ -1613,33 +1619,33 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="B38">
-        <v>-22.0852</v>
+        <v>-25.517744</v>
       </c>
       <c r="C38">
-        <v>-39.827500000000001</v>
+        <v>-43.466293</v>
       </c>
       <c r="D38" t="s">
         <v>28</v>
       </c>
-      <c r="E38" t="s">
-        <v>60</v>
-      </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>105</v>
+      </c>
+      <c r="G38" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39">
-        <v>-21.882000000000001</v>
+        <v>-22.0852</v>
       </c>
       <c r="C39">
-        <v>-39.8598</v>
+        <v>-39.827500000000001</v>
       </c>
       <c r="D39" t="s">
         <v>28</v>
@@ -1650,79 +1656,88 @@
       <c r="F39" t="s">
         <v>31</v>
       </c>
-      <c r="G39" t="s">
-        <v>66</v>
-      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B40">
-        <v>-22.22</v>
+        <v>-21.882000000000001</v>
       </c>
       <c r="C40">
-        <v>-40.33</v>
+        <v>-39.8598</v>
       </c>
       <c r="D40" t="s">
         <v>28</v>
       </c>
+      <c r="E40" t="s">
+        <v>60</v>
+      </c>
       <c r="F40" t="s">
         <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B41">
-        <v>-23.317</v>
+        <v>-22.22</v>
       </c>
       <c r="C41">
-        <v>-41.255200000000002</v>
+        <v>-40.33</v>
       </c>
       <c r="D41" t="s">
         <v>28</v>
       </c>
-      <c r="E41" t="s">
-        <v>60</v>
-      </c>
       <c r="F41" t="s">
         <v>31</v>
       </c>
       <c r="G41" t="s">
-        <v>69</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B42">
-        <v>-22.16</v>
+        <v>-23.317</v>
       </c>
       <c r="C42">
-        <v>-40.14</v>
+        <v>-41.255200000000002</v>
       </c>
       <c r="D42" t="s">
         <v>28</v>
       </c>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F42" t="s">
         <v>31</v>
+      </c>
+      <c r="G42" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>70</v>
+      </c>
+      <c r="B43">
+        <v>-22.16</v>
+      </c>
+      <c r="C43">
+        <v>-40.14</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>28</v>
+      </c>
+      <c r="E43" t="s">
+        <v>56</v>
       </c>
       <c r="F43" t="s">
         <v>31</v>
@@ -1730,92 +1745,92 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>72</v>
-      </c>
-      <c r="B44">
-        <v>-21.33</v>
-      </c>
-      <c r="C44">
-        <v>-40.01</v>
+        <v>71</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
-      </c>
-      <c r="G44" t="s">
-        <v>142</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+      <c r="B45">
+        <v>-21.33</v>
+      </c>
+      <c r="C45">
+        <v>-40.01</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>103</v>
+      </c>
+      <c r="G45" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>74</v>
-      </c>
-      <c r="B46">
-        <v>-21.975999999999999</v>
-      </c>
-      <c r="C46">
-        <v>-39.725000000000001</v>
+        <v>73</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F46" t="s">
         <v>31</v>
-      </c>
-      <c r="G46" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B47">
-        <v>-23.5244</v>
+        <v>-21.975999999999999</v>
       </c>
       <c r="C47">
-        <v>-41.081299999999999</v>
+        <v>-39.725000000000001</v>
       </c>
       <c r="D47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F47" t="s">
         <v>31</v>
       </c>
       <c r="G47" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="B48">
+        <v>-23.5244</v>
+      </c>
+      <c r="C48">
+        <v>-41.081299999999999</v>
       </c>
       <c r="D48" t="s">
         <v>44</v>
       </c>
+      <c r="E48" t="s">
+        <v>45</v>
+      </c>
       <c r="F48" t="s">
         <v>31</v>
+      </c>
+      <c r="G48" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D49" t="s">
         <v>44</v>
@@ -1826,16 +1841,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50">
-        <v>-22.37</v>
-      </c>
-      <c r="C50">
-        <v>-40.04</v>
+        <v>77</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F50" t="s">
         <v>31</v>
@@ -1843,18 +1852,24 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51">
+        <v>-22.37</v>
+      </c>
+      <c r="C51">
+        <v>-40.04</v>
+      </c>
+      <c r="D51" t="s">
+        <v>24</v>
+      </c>
+      <c r="F51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>79</v>
-      </c>
-      <c r="D51" t="s">
-        <v>80</v>
-      </c>
-      <c r="F51" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>81</v>
       </c>
       <c r="D52" t="s">
         <v>80</v>
@@ -1865,18 +1880,18 @@
     </row>
     <row r="53" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" t="s">
+        <v>80</v>
+      </c>
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>82</v>
-      </c>
-      <c r="D53" t="s">
-        <v>49</v>
-      </c>
-      <c r="F53" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>83</v>
       </c>
       <c r="D54" t="s">
         <v>49</v>
@@ -1887,7 +1902,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D55" t="s">
         <v>49</v>
@@ -1898,13 +1913,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>85</v>
-      </c>
-      <c r="B56">
-        <v>-23.39</v>
-      </c>
-      <c r="C56">
-        <v>-41.4</v>
+        <v>84</v>
       </c>
       <c r="D56" t="s">
         <v>49</v>
@@ -1912,13 +1921,16 @@
       <c r="F56" t="s">
         <v>31</v>
       </c>
-      <c r="G56" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+      <c r="B57">
+        <v>-23.39</v>
+      </c>
+      <c r="C57">
+        <v>-41.4</v>
       </c>
       <c r="D57" t="s">
         <v>49</v>
@@ -1926,81 +1938,87 @@
       <c r="F57" t="s">
         <v>31</v>
       </c>
+      <c r="G57" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>87</v>
-      </c>
-      <c r="B58">
-        <v>-22.96</v>
-      </c>
-      <c r="C58">
-        <v>-40.72</v>
+        <v>86</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F58" t="s">
         <v>31</v>
-      </c>
-      <c r="G58" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>87</v>
+      </c>
+      <c r="B59">
+        <v>-22.96</v>
+      </c>
+      <c r="C59">
+        <v>-40.72</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>157</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>-22.672789000000002</v>
       </c>
-      <c r="C59">
+      <c r="C60">
         <v>-40.546345000000002</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D60" t="s">
         <v>80</v>
       </c>
-      <c r="F59" t="s">
-        <v>31</v>
-      </c>
-      <c r="G59" t="s">
+      <c r="F60" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+    <row r="61" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>88</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>-22.13</v>
       </c>
-      <c r="C60">
+      <c r="C61">
         <v>-39.96</v>
       </c>
-      <c r="D60" t="s">
-        <v>28</v>
-      </c>
-      <c r="F60" t="s">
-        <v>31</v>
-      </c>
-      <c r="G60" t="s">
+      <c r="D61" t="s">
+        <v>28</v>
+      </c>
+      <c r="F61" t="s">
+        <v>31</v>
+      </c>
+      <c r="G61" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="4" t="s">
+    <row r="62" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D62" t="s">
         <v>80</v>
-      </c>
-      <c r="F61" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>90</v>
       </c>
       <c r="F62" t="s">
         <v>31</v>
@@ -2008,33 +2026,21 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>91</v>
-      </c>
-      <c r="B63">
-        <v>-22.55</v>
-      </c>
-      <c r="C63">
-        <v>-40.25</v>
-      </c>
-      <c r="D63" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
-      </c>
-      <c r="G63" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B64">
-        <v>-22.34</v>
+        <v>-22.55</v>
       </c>
       <c r="C64">
-        <v>-40.19</v>
+        <v>-40.25</v>
       </c>
       <c r="D64" t="s">
         <v>28</v>
@@ -2043,18 +2049,18 @@
         <v>31</v>
       </c>
       <c r="G64" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B65">
-        <v>-22.66</v>
+        <v>-22.34</v>
       </c>
       <c r="C65">
-        <v>-40.229999999999997</v>
+        <v>-40.19</v>
       </c>
       <c r="D65" t="s">
         <v>28</v>
@@ -2063,23 +2069,32 @@
         <v>31</v>
       </c>
       <c r="G65" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>95</v>
+        <v>93</v>
+      </c>
+      <c r="B66">
+        <v>-22.66</v>
+      </c>
+      <c r="C66">
+        <v>-40.229999999999997</v>
       </c>
       <c r="D66" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F66" t="s">
         <v>31</v>
+      </c>
+      <c r="G66" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D67" t="s">
         <v>80</v>
@@ -2090,67 +2105,61 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D68" t="s">
+        <v>80</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>97</v>
       </c>
-      <c r="B68">
+      <c r="B69">
         <v>-22.42</v>
       </c>
-      <c r="C68">
+      <c r="C69">
         <v>-39.950000000000003</v>
       </c>
-      <c r="D68" t="s">
-        <v>28</v>
-      </c>
-      <c r="F68" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B69">
-        <v>-21.96</v>
-      </c>
-      <c r="C69">
-        <v>-39.82</v>
-      </c>
       <c r="D69" t="s">
         <v>28</v>
       </c>
       <c r="F69" t="s">
         <v>31</v>
-      </c>
-      <c r="G69" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B70">
-        <v>-21.99</v>
+        <v>-21.96</v>
       </c>
       <c r="C70">
-        <v>-39.729999999999997</v>
+        <v>-39.82</v>
       </c>
       <c r="D70" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F70" t="s">
         <v>31</v>
+      </c>
+      <c r="G70" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B71">
-        <v>-22.62</v>
+        <v>-21.99</v>
       </c>
       <c r="C71">
-        <v>-39.979999999999997</v>
+        <v>-39.729999999999997</v>
       </c>
       <c r="D71" t="s">
         <v>80</v>
@@ -2158,79 +2167,76 @@
       <c r="F71" t="s">
         <v>31</v>
       </c>
-      <c r="G71" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B72">
-        <v>-21.23</v>
+        <v>-22.62</v>
       </c>
       <c r="C72">
-        <v>-40.04</v>
+        <v>-39.979999999999997</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="F72" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="G72" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="B73">
-        <v>-22.701767</v>
+        <v>-21.23</v>
       </c>
       <c r="C73">
-        <v>-40.677059</v>
+        <v>-40.04</v>
       </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G73" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="B74">
-        <v>-25.022000999999999</v>
+        <v>-22.701767</v>
       </c>
       <c r="C74">
-        <v>-42.667259000000001</v>
+        <v>-40.677059</v>
       </c>
       <c r="D74" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="F74" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="G74" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="B75">
-        <v>-25.656942000000001</v>
+        <v>-25.022000999999999</v>
       </c>
       <c r="C75">
-        <v>-42.858749000000003</v>
+        <v>-42.667259000000001</v>
       </c>
       <c r="D75" t="s">
         <v>28</v>
@@ -2239,18 +2245,18 @@
         <v>105</v>
       </c>
       <c r="G75" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B76">
-        <v>-24.776168999999999</v>
+        <v>-25.656942000000001</v>
       </c>
       <c r="C76">
-        <v>-42.720005</v>
+        <v>-42.858749000000003</v>
       </c>
       <c r="D76" t="s">
         <v>28</v>
@@ -2259,18 +2265,18 @@
         <v>105</v>
       </c>
       <c r="G76" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="B77">
-        <v>-24.64</v>
+        <v>-24.776168999999999</v>
       </c>
       <c r="C77">
-        <v>-42.51</v>
+        <v>-42.720005</v>
       </c>
       <c r="D77" t="s">
         <v>28</v>
@@ -2279,18 +2285,18 @@
         <v>105</v>
       </c>
       <c r="G77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B78">
-        <v>-24.78</v>
+        <v>-24.64</v>
       </c>
       <c r="C78">
-        <v>-42.5</v>
+        <v>-42.51</v>
       </c>
       <c r="D78" t="s">
         <v>28</v>
@@ -2304,10 +2310,10 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B79">
-        <v>-24.68</v>
+        <v>-24.78</v>
       </c>
       <c r="C79">
         <v>-42.5</v>
@@ -2324,13 +2330,13 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B80">
-        <v>-24.63</v>
+        <v>-24.68</v>
       </c>
       <c r="C80">
-        <v>-42.41</v>
+        <v>-42.5</v>
       </c>
       <c r="D80" t="s">
         <v>28</v>
@@ -2344,13 +2350,13 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B81">
-        <v>-24.67</v>
+        <v>-24.63</v>
       </c>
       <c r="C81">
-        <v>-42.38</v>
+        <v>-42.41</v>
       </c>
       <c r="D81" t="s">
         <v>28</v>
@@ -2364,13 +2370,13 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B82">
-        <v>-24.54</v>
+        <v>-24.67</v>
       </c>
       <c r="C82">
-        <v>-42.46</v>
+        <v>-42.38</v>
       </c>
       <c r="D82" t="s">
         <v>28</v>
@@ -2384,13 +2390,13 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="B83">
-        <v>-24.59</v>
+        <v>-24.54</v>
       </c>
       <c r="C83">
-        <v>-42.56</v>
+        <v>-42.46</v>
       </c>
       <c r="D83" t="s">
         <v>28</v>
@@ -2404,13 +2410,13 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="B84">
-        <v>-24.74</v>
+        <v>-24.59</v>
       </c>
       <c r="C84">
-        <v>-42.51</v>
+        <v>-42.56</v>
       </c>
       <c r="D84" t="s">
         <v>28</v>
@@ -2424,13 +2430,13 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="B85">
-        <v>-25.798373999999999</v>
+        <v>-24.74</v>
       </c>
       <c r="C85">
-        <v>-43.262680000000003</v>
+        <v>-42.51</v>
       </c>
       <c r="D85" t="s">
         <v>28</v>
@@ -2439,18 +2445,18 @@
         <v>105</v>
       </c>
       <c r="G85" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B86">
-        <v>-25.671883000000001</v>
+        <v>-25.798373999999999</v>
       </c>
       <c r="C86">
-        <v>-43.205939999999998</v>
+        <v>-43.262680000000003</v>
       </c>
       <c r="D86" t="s">
         <v>28</v>
@@ -2464,13 +2470,13 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="B87">
-        <v>-25.226118</v>
+        <v>-25.671883000000001</v>
       </c>
       <c r="C87">
-        <v>-42.56982</v>
+        <v>-43.205939999999998</v>
       </c>
       <c r="D87" t="s">
         <v>28</v>
@@ -2479,18 +2485,18 @@
         <v>105</v>
       </c>
       <c r="G87" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B88">
-        <v>-24.685623</v>
+        <v>-25.226118</v>
       </c>
       <c r="C88">
-        <v>-42.293922000000002</v>
+        <v>-42.56982</v>
       </c>
       <c r="D88" t="s">
         <v>28</v>
@@ -2499,60 +2505,72 @@
         <v>105</v>
       </c>
       <c r="G88" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B89">
-        <v>-22.1</v>
+        <v>-24.685623</v>
       </c>
       <c r="C89">
-        <v>-39.909999999999997</v>
+        <v>-42.293922000000002</v>
       </c>
       <c r="D89" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F89" t="s">
-        <v>31</v>
+        <v>105</v>
+      </c>
+      <c r="G89" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B90">
-        <v>-23.08</v>
+        <v>-22.1</v>
       </c>
       <c r="C90">
-        <v>-40.99</v>
+        <v>-39.909999999999997</v>
       </c>
       <c r="D90" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="F90" t="s">
         <v>31</v>
-      </c>
-      <c r="G90" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="B91">
+        <v>-23.08</v>
+      </c>
+      <c r="C91">
+        <v>-40.99</v>
       </c>
       <c r="D91" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
+      </c>
+      <c r="G91" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="D92" t="s">
+        <v>120</v>
       </c>
       <c r="F92" t="s">
         <v>31</v>
@@ -2560,16 +2578,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B93">
-        <v>-22.14</v>
-      </c>
-      <c r="C93">
-        <v>-39.92</v>
-      </c>
-      <c r="D93" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -2577,7 +2586,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B94">
         <v>-22.14</v>
@@ -2594,106 +2603,103 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B95">
-        <v>-23.3827</v>
+        <v>-22.14</v>
       </c>
       <c r="C95">
-        <v>-40.073999999999998</v>
+        <v>-39.92</v>
       </c>
       <c r="D95" t="s">
         <v>24</v>
       </c>
-      <c r="E95" t="s">
-        <v>125</v>
-      </c>
       <c r="F95" t="s">
-        <v>105</v>
-      </c>
-      <c r="G95" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
+      </c>
+      <c r="B96">
+        <v>-23.3827</v>
+      </c>
+      <c r="C96">
+        <v>-40.073999999999998</v>
       </c>
       <c r="D96" t="s">
         <v>24</v>
       </c>
+      <c r="E96" t="s">
+        <v>125</v>
+      </c>
       <c r="F96" t="s">
-        <v>31</v>
+        <v>105</v>
+      </c>
+      <c r="G96" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D97" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F97" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="s">
+      <c r="F98" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F98" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+      <c r="F99" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>130</v>
       </c>
-      <c r="B99">
+      <c r="B100">
         <v>-21.33</v>
       </c>
-      <c r="C99">
+      <c r="C100">
         <v>-40.049999999999997</v>
       </c>
-      <c r="D99" t="s">
-        <v>28</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="D100" t="s">
+        <v>28</v>
+      </c>
+      <c r="E100" t="s">
         <v>131</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F100" t="s">
         <v>132</v>
       </c>
-      <c r="G99" t="s">
+      <c r="G100" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B100">
-        <v>-22.436900000000001</v>
-      </c>
-      <c r="C100">
-        <v>-40.425800000000002</v>
-      </c>
-      <c r="D100" t="s">
-        <v>49</v>
-      </c>
-      <c r="F100" t="s">
-        <v>31</v>
-      </c>
-      <c r="G100" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B101">
-        <v>-22.374779</v>
+        <v>-22.436900000000001</v>
       </c>
       <c r="C101">
-        <v>-40.417454999999997</v>
+        <v>-40.425800000000002</v>
       </c>
       <c r="D101" t="s">
         <v>49</v>
@@ -2702,11 +2708,31 @@
         <v>31</v>
       </c>
       <c r="G101" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B102">
+        <v>-22.374779</v>
+      </c>
+      <c r="C102">
+        <v>-40.417454999999997</v>
+      </c>
+      <c r="D102" t="s">
+        <v>49</v>
+      </c>
+      <c r="F102" t="s">
+        <v>31</v>
+      </c>
+      <c r="G102" t="s">
         <v>154</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G101" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{706D6B2C-5D46-4427-8384-F3B56F7E30D9}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2ACFB59-3F01-47EF-91A5-DDF27FAF5A7C}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>

--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2ACFB59-3F01-47EF-91A5-DDF27FAF5A7C}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7000AF1C-0D4C-418B-9E16-0C1FCA86C439}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$110</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="169">
   <si>
     <t>unidade</t>
   </si>
@@ -517,6 +517,33 @@
   </si>
   <si>
     <t>lapa</t>
+  </si>
+  <si>
+    <t>PETROBRAS 67 (P-67)</t>
+  </si>
+  <si>
+    <t>PETROBRAS 66 (P-66)</t>
+  </si>
+  <si>
+    <t>FPSO CIDADE ANGRA DOS REIS</t>
+  </si>
+  <si>
+    <t>FPSO CIDADE ITAGUAI</t>
+  </si>
+  <si>
+    <t>north sea</t>
+  </si>
+  <si>
+    <t>FPSO CIDADE MARICA</t>
+  </si>
+  <si>
+    <t>FPSO CIDADE PARATY</t>
+  </si>
+  <si>
+    <t>FPSO CIDADE MANGARATIBA</t>
+  </si>
+  <si>
+    <t>FPSO CIDADE SAQUAREMA</t>
   </si>
 </sst>
 </file>
@@ -932,17 +959,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G102"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G110"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.88671875" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -965,7 +992,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -982,7 +1009,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -999,7 +1026,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1016,7 +1043,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1033,7 +1060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1050,7 +1077,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1067,7 +1094,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1084,7 +1111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -1101,7 +1128,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -1118,7 +1145,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1135,7 +1162,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -1152,7 +1179,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1169,7 +1196,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1186,7 +1213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1206,7 +1233,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
@@ -1226,7 +1253,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>30</v>
       </c>
@@ -1246,7 +1273,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -1264,7 +1291,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>33</v>
       </c>
@@ -1281,7 +1308,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1304,7 +1331,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
@@ -1327,7 +1354,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>39</v>
       </c>
@@ -1347,7 +1374,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>40</v>
       </c>
@@ -1361,7 +1388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -1384,7 +1411,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -1404,7 +1431,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1421,7 +1448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -1441,7 +1468,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>48</v>
       </c>
@@ -1452,7 +1479,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -1463,7 +1490,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -1483,7 +1510,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -1503,7 +1530,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>53</v>
       </c>
@@ -1514,7 +1541,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -1531,7 +1558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -1551,7 +1578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -1571,7 +1598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -1594,7 +1621,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -1617,495 +1644,528 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38">
+        <v>54.109959000000003</v>
+      </c>
+      <c r="C38">
+        <v>7.4783869999999997</v>
+      </c>
+      <c r="D38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" t="s">
+        <v>164</v>
+      </c>
+      <c r="G38" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39">
+        <v>-25.139942000000001</v>
+      </c>
+      <c r="C39">
+        <v>-42.944110999999999</v>
+      </c>
+      <c r="D39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" t="s">
+        <v>56</v>
+      </c>
+      <c r="F39" t="s">
+        <v>105</v>
+      </c>
+      <c r="G39" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B40">
+        <v>-25.393484000000001</v>
+      </c>
+      <c r="C40">
+        <v>-42.761291999999997</v>
+      </c>
+      <c r="D40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" t="s">
+        <v>105</v>
+      </c>
+      <c r="G40" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41">
+        <v>-25.202905999999999</v>
+      </c>
+      <c r="C41">
+        <v>-42.878483000000003</v>
+      </c>
+      <c r="D41" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" t="s">
+        <v>105</v>
+      </c>
+      <c r="G41" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42">
+        <v>-25.447762999999998</v>
+      </c>
+      <c r="C42">
+        <v>-42.752960000000002</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" t="s">
+        <v>105</v>
+      </c>
+      <c r="G42" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>168</v>
+      </c>
+      <c r="B43">
+        <v>-25.490202</v>
+      </c>
+      <c r="C43">
+        <v>-42.781055000000002</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" t="s">
+        <v>105</v>
+      </c>
+      <c r="G43" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>158</v>
       </c>
-      <c r="B38">
+      <c r="B44">
         <v>-25.517744</v>
       </c>
-      <c r="C38">
+      <c r="C44">
         <v>-43.466293</v>
       </c>
-      <c r="D38" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="D44" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" t="s">
         <v>105</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G44" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>64</v>
       </c>
-      <c r="B39">
+      <c r="B45">
         <v>-22.0852</v>
       </c>
-      <c r="C39">
+      <c r="C45">
         <v>-39.827500000000001</v>
       </c>
-      <c r="D39" t="s">
-        <v>28</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="D45" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" t="s">
         <v>60</v>
       </c>
-      <c r="F39" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>65</v>
       </c>
-      <c r="B40">
+      <c r="B46">
         <v>-21.882000000000001</v>
       </c>
-      <c r="C40">
+      <c r="C46">
         <v>-39.8598</v>
       </c>
-      <c r="D40" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="D46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" t="s">
         <v>60</v>
       </c>
-      <c r="F40" t="s">
-        <v>31</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>67</v>
       </c>
-      <c r="B41">
+      <c r="B47">
         <v>-22.22</v>
       </c>
-      <c r="C41">
+      <c r="C47">
         <v>-40.33</v>
       </c>
-      <c r="D41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F41" t="s">
-        <v>31</v>
-      </c>
-      <c r="G41" t="s">
+      <c r="D47" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>68</v>
       </c>
-      <c r="B42">
+      <c r="B48">
         <v>-23.317</v>
       </c>
-      <c r="C42">
+      <c r="C48">
         <v>-41.255200000000002</v>
       </c>
-      <c r="D42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="D48" t="s">
+        <v>28</v>
+      </c>
+      <c r="E48" t="s">
         <v>60</v>
       </c>
-      <c r="F42" t="s">
-        <v>31</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>70</v>
       </c>
-      <c r="B43">
+      <c r="B49">
         <v>-22.16</v>
       </c>
-      <c r="C43">
+      <c r="C49">
         <v>-40.14</v>
       </c>
-      <c r="D43" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="D49" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" t="s">
         <v>56</v>
       </c>
-      <c r="F43" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>71</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D50" t="s">
         <v>49</v>
       </c>
-      <c r="F44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>72</v>
       </c>
-      <c r="B45">
+      <c r="B51">
         <v>-21.33</v>
       </c>
-      <c r="C45">
+      <c r="C51">
         <v>-40.01</v>
-      </c>
-      <c r="D45" t="s">
-        <v>24</v>
-      </c>
-      <c r="F45" t="s">
-        <v>103</v>
-      </c>
-      <c r="G45" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>73</v>
-      </c>
-      <c r="D46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F46" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>74</v>
-      </c>
-      <c r="B47">
-        <v>-21.975999999999999</v>
-      </c>
-      <c r="C47">
-        <v>-39.725000000000001</v>
-      </c>
-      <c r="D47" t="s">
-        <v>24</v>
-      </c>
-      <c r="F47" t="s">
-        <v>31</v>
-      </c>
-      <c r="G47" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48">
-        <v>-23.5244</v>
-      </c>
-      <c r="C48">
-        <v>-41.081299999999999</v>
-      </c>
-      <c r="D48" t="s">
-        <v>44</v>
-      </c>
-      <c r="E48" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G48" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>77</v>
-      </c>
-      <c r="D50" t="s">
-        <v>44</v>
-      </c>
-      <c r="F50" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>78</v>
-      </c>
-      <c r="B51">
-        <v>-22.37</v>
-      </c>
-      <c r="C51">
-        <v>-40.04</v>
       </c>
       <c r="D51" t="s">
         <v>24</v>
       </c>
       <c r="F51" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+      <c r="G51" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52" t="s">
+        <v>44</v>
+      </c>
+      <c r="F52" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53">
+        <v>-21.975999999999999</v>
+      </c>
+      <c r="C53">
+        <v>-39.725000000000001</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54">
+        <v>-23.5244</v>
+      </c>
+      <c r="C54">
+        <v>-41.081299999999999</v>
+      </c>
+      <c r="D54" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" t="s">
+        <v>45</v>
+      </c>
+      <c r="F54" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55" t="s">
+        <v>44</v>
+      </c>
+      <c r="F55" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>78</v>
+      </c>
+      <c r="B57">
+        <v>-22.37</v>
+      </c>
+      <c r="C57">
+        <v>-40.04</v>
+      </c>
+      <c r="D57" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>79</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D58" t="s">
         <v>80</v>
       </c>
-      <c r="F52" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>81</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D59" t="s">
         <v>80</v>
       </c>
-      <c r="F53" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>82</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D60" t="s">
         <v>49</v>
       </c>
-      <c r="F54" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="F60" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>83</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D61" t="s">
         <v>49</v>
       </c>
-      <c r="F55" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="F61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>84</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D62" t="s">
         <v>49</v>
       </c>
-      <c r="F56" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="F62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>85</v>
       </c>
-      <c r="B57">
+      <c r="B63">
         <v>-23.39</v>
       </c>
-      <c r="C57">
+      <c r="C63">
         <v>-41.4</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D63" t="s">
         <v>49</v>
       </c>
-      <c r="F57" t="s">
-        <v>31</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="F63" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>86</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D64" t="s">
         <v>49</v>
       </c>
-      <c r="F58" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="F64" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>87</v>
       </c>
-      <c r="B59">
+      <c r="B65">
         <v>-22.96</v>
       </c>
-      <c r="C59">
+      <c r="C65">
         <v>-40.72</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D65" t="s">
         <v>24</v>
       </c>
-      <c r="F59" t="s">
-        <v>31</v>
-      </c>
-      <c r="G59" t="s">
+      <c r="F65" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>157</v>
       </c>
-      <c r="B60">
+      <c r="B66">
         <v>-22.672789000000002</v>
       </c>
-      <c r="C60">
+      <c r="C66">
         <v>-40.546345000000002</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D66" t="s">
         <v>80</v>
       </c>
-      <c r="F60" t="s">
-        <v>31</v>
-      </c>
-      <c r="G60" t="s">
+      <c r="F66" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+    <row r="67" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>88</v>
       </c>
-      <c r="B61">
+      <c r="B67">
         <v>-22.13</v>
       </c>
-      <c r="C61">
+      <c r="C67">
         <v>-39.96</v>
       </c>
-      <c r="D61" t="s">
-        <v>28</v>
-      </c>
-      <c r="F61" t="s">
-        <v>31</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="D67" t="s">
+        <v>28</v>
+      </c>
+      <c r="F67" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="4" t="s">
+    <row r="68" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="D62" t="s">
-        <v>80</v>
-      </c>
-      <c r="F62" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>90</v>
-      </c>
-      <c r="F63" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>91</v>
-      </c>
-      <c r="B64">
-        <v>-22.55</v>
-      </c>
-      <c r="C64">
-        <v>-40.25</v>
-      </c>
-      <c r="D64" t="s">
-        <v>28</v>
-      </c>
-      <c r="F64" t="s">
-        <v>31</v>
-      </c>
-      <c r="G64" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>92</v>
-      </c>
-      <c r="B65">
-        <v>-22.34</v>
-      </c>
-      <c r="C65">
-        <v>-40.19</v>
-      </c>
-      <c r="D65" t="s">
-        <v>28</v>
-      </c>
-      <c r="F65" t="s">
-        <v>31</v>
-      </c>
-      <c r="G65" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>93</v>
-      </c>
-      <c r="B66">
-        <v>-22.66</v>
-      </c>
-      <c r="C66">
-        <v>-40.229999999999997</v>
-      </c>
-      <c r="D66" t="s">
-        <v>28</v>
-      </c>
-      <c r="F66" t="s">
-        <v>31</v>
-      </c>
-      <c r="G66" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>95</v>
-      </c>
-      <c r="D67" t="s">
-        <v>80</v>
-      </c>
-      <c r="F67" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>96</v>
       </c>
       <c r="D68" t="s">
         <v>80</v>
@@ -2114,32 +2174,23 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>97</v>
-      </c>
-      <c r="B69">
-        <v>-22.42</v>
-      </c>
-      <c r="C69">
-        <v>-39.950000000000003</v>
-      </c>
-      <c r="D69" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F69" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
-        <v>98</v>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>91</v>
       </c>
       <c r="B70">
-        <v>-21.96</v>
+        <v>-22.55</v>
       </c>
       <c r="C70">
-        <v>-39.82</v>
+        <v>-40.25</v>
       </c>
       <c r="D70" t="s">
         <v>28</v>
@@ -2148,75 +2199,63 @@
         <v>31</v>
       </c>
       <c r="G70" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
-        <v>99</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>92</v>
       </c>
       <c r="B71">
-        <v>-21.99</v>
+        <v>-22.34</v>
       </c>
       <c r="C71">
-        <v>-39.729999999999997</v>
+        <v>-40.19</v>
       </c>
       <c r="D71" t="s">
+        <v>28</v>
+      </c>
+      <c r="F71" t="s">
+        <v>31</v>
+      </c>
+      <c r="G71" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>93</v>
+      </c>
+      <c r="B72">
+        <v>-22.66</v>
+      </c>
+      <c r="C72">
+        <v>-40.229999999999997</v>
+      </c>
+      <c r="D72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72" t="s">
+        <v>31</v>
+      </c>
+      <c r="G72" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>95</v>
+      </c>
+      <c r="D73" t="s">
         <v>80</v>
       </c>
-      <c r="F71" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B72">
-        <v>-22.62</v>
-      </c>
-      <c r="C72">
-        <v>-39.979999999999997</v>
-      </c>
-      <c r="D72" t="s">
-        <v>80</v>
-      </c>
-      <c r="F72" t="s">
-        <v>31</v>
-      </c>
-      <c r="G72" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B73">
-        <v>-21.23</v>
-      </c>
-      <c r="C73">
-        <v>-40.04</v>
-      </c>
-      <c r="D73" t="s">
-        <v>28</v>
-      </c>
       <c r="F73" t="s">
-        <v>103</v>
-      </c>
-      <c r="G73" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B74">
-        <v>-22.701767</v>
-      </c>
-      <c r="C74">
-        <v>-40.677059</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>96</v>
       </c>
       <c r="D74" t="s">
         <v>80</v>
@@ -2224,139 +2263,130 @@
       <c r="F74" t="s">
         <v>31</v>
       </c>
-      <c r="G74" t="s">
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>97</v>
+      </c>
+      <c r="B75">
+        <v>-22.42</v>
+      </c>
+      <c r="C75">
+        <v>-39.950000000000003</v>
+      </c>
+      <c r="D75" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B76">
+        <v>-21.96</v>
+      </c>
+      <c r="C76">
+        <v>-39.82</v>
+      </c>
+      <c r="D76" t="s">
+        <v>28</v>
+      </c>
+      <c r="F76" t="s">
+        <v>31</v>
+      </c>
+      <c r="G76" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B77">
+        <v>-21.99</v>
+      </c>
+      <c r="C77">
+        <v>-39.729999999999997</v>
+      </c>
+      <c r="D77" t="s">
+        <v>80</v>
+      </c>
+      <c r="F77" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B78">
+        <v>-22.62</v>
+      </c>
+      <c r="C78">
+        <v>-39.979999999999997</v>
+      </c>
+      <c r="D78" t="s">
+        <v>80</v>
+      </c>
+      <c r="F78" t="s">
+        <v>31</v>
+      </c>
+      <c r="G78" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B79">
+        <v>-21.23</v>
+      </c>
+      <c r="C79">
+        <v>-40.04</v>
+      </c>
+      <c r="D79" t="s">
+        <v>28</v>
+      </c>
+      <c r="F79" t="s">
+        <v>103</v>
+      </c>
+      <c r="G79" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80">
+        <v>-22.701767</v>
+      </c>
+      <c r="C80">
+        <v>-40.677059</v>
+      </c>
+      <c r="D80" t="s">
+        <v>80</v>
+      </c>
+      <c r="F80" t="s">
+        <v>31</v>
+      </c>
+      <c r="G80" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B75">
-        <v>-25.022000999999999</v>
-      </c>
-      <c r="C75">
-        <v>-42.667259000000001</v>
-      </c>
-      <c r="D75" t="s">
-        <v>28</v>
-      </c>
-      <c r="F75" t="s">
-        <v>105</v>
-      </c>
-      <c r="G75" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B76">
-        <v>-25.656942000000001</v>
-      </c>
-      <c r="C76">
-        <v>-42.858749000000003</v>
-      </c>
-      <c r="D76" t="s">
-        <v>28</v>
-      </c>
-      <c r="F76" t="s">
-        <v>105</v>
-      </c>
-      <c r="G76" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B77">
-        <v>-24.776168999999999</v>
-      </c>
-      <c r="C77">
-        <v>-42.720005</v>
-      </c>
-      <c r="D77" t="s">
-        <v>28</v>
-      </c>
-      <c r="F77" t="s">
-        <v>105</v>
-      </c>
-      <c r="G77" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B78">
-        <v>-24.64</v>
-      </c>
-      <c r="C78">
-        <v>-42.51</v>
-      </c>
-      <c r="D78" t="s">
-        <v>28</v>
-      </c>
-      <c r="F78" t="s">
-        <v>105</v>
-      </c>
-      <c r="G78" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B79">
-        <v>-24.78</v>
-      </c>
-      <c r="C79">
-        <v>-42.5</v>
-      </c>
-      <c r="D79" t="s">
-        <v>28</v>
-      </c>
-      <c r="F79" t="s">
-        <v>105</v>
-      </c>
-      <c r="G79" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B80">
-        <v>-24.68</v>
-      </c>
-      <c r="C80">
-        <v>-42.5</v>
-      </c>
-      <c r="D80" t="s">
-        <v>28</v>
-      </c>
-      <c r="F80" t="s">
-        <v>105</v>
-      </c>
-      <c r="G80" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B81">
-        <v>-24.63</v>
+        <v>-25.601856000000002</v>
       </c>
       <c r="C81">
-        <v>-42.41</v>
+        <v>-42.820484</v>
       </c>
       <c r="D81" t="s">
         <v>28</v>
@@ -2365,18 +2395,18 @@
         <v>105</v>
       </c>
       <c r="G81" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B82">
-        <v>-24.67</v>
+        <v>-25.328738999999999</v>
       </c>
       <c r="C82">
-        <v>-42.38</v>
+        <v>-42.692242</v>
       </c>
       <c r="D82" t="s">
         <v>28</v>
@@ -2385,18 +2415,18 @@
         <v>105</v>
       </c>
       <c r="G82" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B83">
-        <v>-24.54</v>
+        <v>-25.022000999999999</v>
       </c>
       <c r="C83">
-        <v>-42.46</v>
+        <v>-42.667259000000001</v>
       </c>
       <c r="D83" t="s">
         <v>28</v>
@@ -2405,18 +2435,18 @@
         <v>105</v>
       </c>
       <c r="G83" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B84">
-        <v>-24.59</v>
+        <v>-25.656942000000001</v>
       </c>
       <c r="C84">
-        <v>-42.56</v>
+        <v>-42.858749000000003</v>
       </c>
       <c r="D84" t="s">
         <v>28</v>
@@ -2425,18 +2455,18 @@
         <v>105</v>
       </c>
       <c r="G84" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="B85">
-        <v>-24.74</v>
+        <v>-24.776168999999999</v>
       </c>
       <c r="C85">
-        <v>-42.51</v>
+        <v>-42.720005</v>
       </c>
       <c r="D85" t="s">
         <v>28</v>
@@ -2445,18 +2475,18 @@
         <v>105</v>
       </c>
       <c r="G85" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="B86">
-        <v>-25.798373999999999</v>
+        <v>-24.64</v>
       </c>
       <c r="C86">
-        <v>-43.262680000000003</v>
+        <v>-42.51</v>
       </c>
       <c r="D86" t="s">
         <v>28</v>
@@ -2465,18 +2495,18 @@
         <v>105</v>
       </c>
       <c r="G86" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="B87">
-        <v>-25.671883000000001</v>
+        <v>-24.78</v>
       </c>
       <c r="C87">
-        <v>-43.205939999999998</v>
+        <v>-42.5</v>
       </c>
       <c r="D87" t="s">
         <v>28</v>
@@ -2485,18 +2515,18 @@
         <v>105</v>
       </c>
       <c r="G87" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B88">
-        <v>-25.226118</v>
+        <v>-24.68</v>
       </c>
       <c r="C88">
-        <v>-42.56982</v>
+        <v>-42.5</v>
       </c>
       <c r="D88" t="s">
         <v>28</v>
@@ -2505,18 +2535,18 @@
         <v>105</v>
       </c>
       <c r="G88" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="B89">
-        <v>-24.685623</v>
+        <v>-24.63</v>
       </c>
       <c r="C89">
-        <v>-42.293922000000002</v>
+        <v>-42.41</v>
       </c>
       <c r="D89" t="s">
         <v>28</v>
@@ -2525,214 +2555,374 @@
         <v>105</v>
       </c>
       <c r="G89" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="B90">
-        <v>-22.1</v>
+        <v>-24.67</v>
       </c>
       <c r="C90">
-        <v>-39.909999999999997</v>
+        <v>-42.38</v>
       </c>
       <c r="D90" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F90" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="G90" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B91">
-        <v>-23.08</v>
+        <v>-24.54</v>
       </c>
       <c r="C91">
-        <v>-40.99</v>
+        <v>-42.46</v>
       </c>
       <c r="D91" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="F91" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="G91" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>119</v>
+        <v>110</v>
+      </c>
+      <c r="B92">
+        <v>-24.59</v>
+      </c>
+      <c r="C92">
+        <v>-42.56</v>
       </c>
       <c r="D92" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="F92" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="G92" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>121</v>
+        <v>149</v>
+      </c>
+      <c r="B93">
+        <v>-24.74</v>
+      </c>
+      <c r="C93">
+        <v>-42.51</v>
+      </c>
+      <c r="D93" t="s">
+        <v>28</v>
       </c>
       <c r="F93" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="G93" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B94">
-        <v>-22.14</v>
+        <v>-25.798373999999999</v>
       </c>
       <c r="C94">
-        <v>-39.92</v>
+        <v>-43.262680000000003</v>
       </c>
       <c r="D94" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F94" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="G94" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B95">
-        <v>-22.14</v>
+        <v>-25.671883000000001</v>
       </c>
       <c r="C95">
-        <v>-39.92</v>
+        <v>-43.205939999999998</v>
       </c>
       <c r="D95" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F95" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="G95" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B96">
-        <v>-23.3827</v>
+        <v>-25.226118</v>
       </c>
       <c r="C96">
-        <v>-40.073999999999998</v>
+        <v>-42.56982</v>
       </c>
       <c r="D96" t="s">
-        <v>24</v>
-      </c>
-      <c r="E96" t="s">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="F96" t="s">
         <v>105</v>
       </c>
       <c r="G96" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B97">
+        <v>-24.685623</v>
+      </c>
+      <c r="C97">
+        <v>-42.293922000000002</v>
+      </c>
+      <c r="D97" t="s">
+        <v>28</v>
+      </c>
+      <c r="F97" t="s">
+        <v>105</v>
+      </c>
+      <c r="G97" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B98">
+        <v>-22.1</v>
+      </c>
+      <c r="C98">
+        <v>-39.909999999999997</v>
+      </c>
+      <c r="D98" t="s">
+        <v>80</v>
+      </c>
+      <c r="F98" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B99">
+        <v>-23.08</v>
+      </c>
+      <c r="C99">
+        <v>-40.99</v>
+      </c>
+      <c r="D99" t="s">
+        <v>49</v>
+      </c>
+      <c r="F99" t="s">
+        <v>31</v>
+      </c>
+      <c r="G99" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D100" t="s">
+        <v>120</v>
+      </c>
+      <c r="F100" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F101" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B102">
+        <v>-22.14</v>
+      </c>
+      <c r="C102">
+        <v>-39.92</v>
+      </c>
+      <c r="D102" t="s">
+        <v>24</v>
+      </c>
+      <c r="F102" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B103">
+        <v>-22.14</v>
+      </c>
+      <c r="C103">
+        <v>-39.92</v>
+      </c>
+      <c r="D103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F103" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B104">
+        <v>-23.3827</v>
+      </c>
+      <c r="C104">
+        <v>-40.073999999999998</v>
+      </c>
+      <c r="D104" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104" t="s">
+        <v>125</v>
+      </c>
+      <c r="F104" t="s">
+        <v>105</v>
+      </c>
+      <c r="G104" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="5" t="s">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D105" t="s">
         <v>24</v>
       </c>
-      <c r="F97" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="s">
+      <c r="F105" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F98" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
+      <c r="F106" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F99" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="F107" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>130</v>
       </c>
-      <c r="B100">
+      <c r="B108">
         <v>-21.33</v>
       </c>
-      <c r="C100">
+      <c r="C108">
         <v>-40.049999999999997</v>
       </c>
-      <c r="D100" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" t="s">
+      <c r="D108" t="s">
+        <v>28</v>
+      </c>
+      <c r="E108" t="s">
         <v>131</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F108" t="s">
         <v>132</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G108" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="s">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B101">
+      <c r="B109">
         <v>-22.436900000000001</v>
       </c>
-      <c r="C101">
+      <c r="C109">
         <v>-40.425800000000002</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D109" t="s">
         <v>49</v>
       </c>
-      <c r="F101" t="s">
-        <v>31</v>
-      </c>
-      <c r="G101" t="s">
+      <c r="F109" t="s">
+        <v>31</v>
+      </c>
+      <c r="G109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="5" t="s">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B102">
+      <c r="B110">
         <v>-22.374779</v>
       </c>
-      <c r="C102">
+      <c r="C110">
         <v>-40.417454999999997</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D110" t="s">
         <v>49</v>
       </c>
-      <c r="F102" t="s">
-        <v>31</v>
-      </c>
-      <c r="G102" t="s">
+      <c r="F110" t="s">
+        <v>31</v>
+      </c>
+      <c r="G110" t="s">
         <v>154</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G110" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2740,7 +2930,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A458B0-5351-487A-ABCF-BB5088AD3353}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7000AF1C-0D4C-418B-9E16-0C1FCA86C439}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A650D45-937E-4FFB-809D-0F245D20853A}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$113</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="178">
   <si>
     <t>unidade</t>
   </si>
@@ -276,15 +276,9 @@
     <t>ODN I (NS41)</t>
   </si>
   <si>
-    <t>P- 65 (P-65)</t>
-  </si>
-  <si>
     <t>Semi-Sub/Produção</t>
   </si>
   <si>
-    <t>P- VIII</t>
-  </si>
-  <si>
     <t>PAMPO 1 (PPM-1)</t>
   </si>
   <si>
@@ -544,6 +538,39 @@
   </si>
   <si>
     <t>FPSO CIDADE SAQUAREMA</t>
+  </si>
+  <si>
+    <t>PETROBRAS 70 (P-70)</t>
+  </si>
+  <si>
+    <t>atapu</t>
+  </si>
+  <si>
+    <t>PETROBRAS 84 (P-84)</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>NORBE IX</t>
+  </si>
+  <si>
+    <t>ODN II</t>
+  </si>
+  <si>
+    <t>amapa</t>
+  </si>
+  <si>
+    <t>morpho</t>
+  </si>
+  <si>
+    <t>NORBE VI</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>FORSEA</t>
   </si>
 </sst>
 </file>
@@ -959,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" customWidth="1"/>
@@ -1125,7 +1152,7 @@
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1142,7 +1169,7 @@
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1159,7 +1186,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1368,10 +1395,10 @@
         <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1465,7 +1492,7 @@
         <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1507,7 +1534,7 @@
         <v>31</v>
       </c>
       <c r="G30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1524,10 +1551,10 @@
         <v>24</v>
       </c>
       <c r="F31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G31" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1646,7 +1673,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B38">
         <v>54.109959000000003</v>
@@ -1658,15 +1685,15 @@
         <v>28</v>
       </c>
       <c r="F38" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G38" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B39">
         <v>-25.139942000000001</v>
@@ -1681,15 +1708,15 @@
         <v>56</v>
       </c>
       <c r="F39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B40">
         <v>-25.393484000000001</v>
@@ -1701,15 +1728,15 @@
         <v>28</v>
       </c>
       <c r="F40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B41">
         <v>-25.202905999999999</v>
@@ -1721,15 +1748,15 @@
         <v>28</v>
       </c>
       <c r="F41" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G41" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B42">
         <v>-25.447762999999998</v>
@@ -1741,15 +1768,15 @@
         <v>28</v>
       </c>
       <c r="F42" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G42" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B43">
         <v>-25.490202</v>
@@ -1761,15 +1788,15 @@
         <v>28</v>
       </c>
       <c r="F43" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G43" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B44">
         <v>-25.517744</v>
@@ -1781,10 +1808,10 @@
         <v>28</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1847,7 +1874,7 @@
         <v>31</v>
       </c>
       <c r="G47" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1918,10 +1945,10 @@
         <v>24</v>
       </c>
       <c r="F51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G51" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1993,66 +2020,114 @@
       <c r="A56" t="s">
         <v>77</v>
       </c>
+      <c r="B56">
+        <v>-21.942143999999999</v>
+      </c>
+      <c r="C56">
+        <v>-39.726315</v>
+      </c>
       <c r="D56" t="s">
         <v>44</v>
       </c>
+      <c r="E56" t="s">
+        <v>177</v>
+      </c>
       <c r="F56" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="B57">
-        <v>-22.37</v>
+        <v>-21.245633999999999</v>
       </c>
       <c r="C57">
-        <v>-40.04</v>
+        <v>-40.031886999999998</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
       </c>
+      <c r="E57" t="s">
+        <v>177</v>
+      </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>176</v>
+      </c>
+      <c r="G57" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>171</v>
+      </c>
+      <c r="B58">
+        <v>-25.246302</v>
+      </c>
+      <c r="C58">
+        <v>-42.538494</v>
       </c>
       <c r="D58" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" t="s">
+        <v>177</v>
+      </c>
+      <c r="F58" t="s">
+        <v>103</v>
+      </c>
+      <c r="G58" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59">
+        <v>-22.37</v>
+      </c>
+      <c r="C59">
+        <v>-40.04</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" t="s">
+        <v>177</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>172</v>
+      </c>
+      <c r="B60">
+        <v>5.2855800000000004</v>
+      </c>
+      <c r="C60">
+        <v>-50.104092000000001</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" t="s">
+        <v>177</v>
+      </c>
+      <c r="F60" t="s">
+        <v>173</v>
+      </c>
+      <c r="G60" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>80</v>
-      </c>
-      <c r="F58" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>81</v>
-      </c>
-      <c r="D59" t="s">
-        <v>80</v>
-      </c>
-      <c r="F59" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" t="s">
-        <v>49</v>
-      </c>
-      <c r="F60" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>83</v>
       </c>
       <c r="D61" t="s">
         <v>49</v>
@@ -2063,7 +2138,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D62" t="s">
         <v>49</v>
@@ -2074,13 +2149,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>85</v>
-      </c>
-      <c r="B63">
-        <v>-23.39</v>
-      </c>
-      <c r="C63">
-        <v>-41.4</v>
+        <v>82</v>
       </c>
       <c r="D63" t="s">
         <v>49</v>
@@ -2088,13 +2157,16 @@
       <c r="F63" t="s">
         <v>31</v>
       </c>
-      <c r="G63" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>83</v>
+      </c>
+      <c r="B64">
+        <v>-23.39</v>
+      </c>
+      <c r="C64">
+        <v>-41.4</v>
       </c>
       <c r="D64" t="s">
         <v>49</v>
@@ -2102,81 +2174,87 @@
       <c r="F64" t="s">
         <v>31</v>
       </c>
+      <c r="G64" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>87</v>
-      </c>
-      <c r="B65">
-        <v>-22.96</v>
-      </c>
-      <c r="C65">
-        <v>-40.72</v>
+        <v>84</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F65" t="s">
         <v>31</v>
-      </c>
-      <c r="G65" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="B66">
+        <v>-22.96</v>
+      </c>
+      <c r="C66">
+        <v>-40.72</v>
+      </c>
+      <c r="D66" t="s">
+        <v>24</v>
+      </c>
+      <c r="F66" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67">
         <v>-22.672789000000002</v>
       </c>
-      <c r="C66">
+      <c r="C67">
         <v>-40.546345000000002</v>
       </c>
-      <c r="D66" t="s">
-        <v>80</v>
-      </c>
-      <c r="F66" t="s">
-        <v>31</v>
-      </c>
-      <c r="G66" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>88</v>
-      </c>
-      <c r="B67">
+      <c r="D67" t="s">
+        <v>79</v>
+      </c>
+      <c r="F67" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>86</v>
+      </c>
+      <c r="B68">
         <v>-22.13</v>
       </c>
-      <c r="C67">
+      <c r="C68">
         <v>-39.96</v>
       </c>
-      <c r="D67" t="s">
-        <v>28</v>
-      </c>
-      <c r="F67" t="s">
-        <v>31</v>
-      </c>
-      <c r="G67" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="D68" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F68" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>90</v>
+      <c r="G68" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D69" t="s">
+        <v>79</v>
       </c>
       <c r="F69" t="s">
         <v>31</v>
@@ -2184,33 +2262,21 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>91</v>
-      </c>
-      <c r="B70">
-        <v>-22.55</v>
-      </c>
-      <c r="C70">
-        <v>-40.25</v>
-      </c>
-      <c r="D70" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="F70" t="s">
         <v>31</v>
-      </c>
-      <c r="G70" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B71">
-        <v>-22.34</v>
+        <v>-22.55</v>
       </c>
       <c r="C71">
-        <v>-40.19</v>
+        <v>-40.25</v>
       </c>
       <c r="D71" t="s">
         <v>28</v>
@@ -2219,18 +2285,18 @@
         <v>31</v>
       </c>
       <c r="G71" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B72">
-        <v>-22.66</v>
+        <v>-22.34</v>
       </c>
       <c r="C72">
-        <v>-40.229999999999997</v>
+        <v>-40.19</v>
       </c>
       <c r="D72" t="s">
         <v>28</v>
@@ -2239,26 +2305,35 @@
         <v>31</v>
       </c>
       <c r="G72" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>95</v>
+        <v>91</v>
+      </c>
+      <c r="B73">
+        <v>-22.66</v>
+      </c>
+      <c r="C73">
+        <v>-40.229999999999997</v>
       </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F73" t="s">
         <v>31</v>
+      </c>
+      <c r="G73" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F74" t="s">
         <v>31</v>
@@ -2266,509 +2341,521 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>97</v>
-      </c>
-      <c r="B75">
+        <v>94</v>
+      </c>
+      <c r="D75" t="s">
+        <v>79</v>
+      </c>
+      <c r="F75" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>95</v>
+      </c>
+      <c r="B76">
         <v>-22.42</v>
       </c>
-      <c r="C75">
+      <c r="C76">
         <v>-39.950000000000003</v>
       </c>
-      <c r="D75" t="s">
-        <v>28</v>
-      </c>
-      <c r="F75" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B76">
-        <v>-21.96</v>
-      </c>
-      <c r="C76">
-        <v>-39.82</v>
-      </c>
       <c r="D76" t="s">
         <v>28</v>
       </c>
       <c r="F76" t="s">
         <v>31</v>
-      </c>
-      <c r="G76" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B77">
-        <v>-21.99</v>
+        <v>-21.96</v>
       </c>
       <c r="C77">
-        <v>-39.729999999999997</v>
+        <v>-39.82</v>
       </c>
       <c r="D77" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F77" t="s">
         <v>31</v>
+      </c>
+      <c r="G77" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B78">
-        <v>-22.62</v>
+        <v>-21.99</v>
       </c>
       <c r="C78">
-        <v>-39.979999999999997</v>
+        <v>-39.729999999999997</v>
       </c>
       <c r="D78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F78" t="s">
         <v>31</v>
-      </c>
-      <c r="G78" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B79">
-        <v>-21.23</v>
+        <v>-22.62</v>
       </c>
       <c r="C79">
-        <v>-40.04</v>
+        <v>-39.979999999999997</v>
       </c>
       <c r="D79" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F79" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="G79" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="B80">
-        <v>-22.701767</v>
+        <v>-21.23</v>
       </c>
       <c r="C80">
-        <v>-40.677059</v>
+        <v>-40.04</v>
       </c>
       <c r="D80" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F80" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="G80" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B81">
-        <v>-25.601856000000002</v>
+        <v>-22.701767</v>
       </c>
       <c r="C81">
-        <v>-42.820484</v>
+        <v>-40.677059</v>
       </c>
       <c r="D81" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="G81" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B82">
-        <v>-25.328738999999999</v>
+        <v>-25.601856000000002</v>
       </c>
       <c r="C82">
-        <v>-42.692242</v>
+        <v>-42.820484</v>
       </c>
       <c r="D82" t="s">
         <v>28</v>
       </c>
       <c r="F82" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G82" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B83">
-        <v>-25.022000999999999</v>
+        <v>-25.328738999999999</v>
       </c>
       <c r="C83">
-        <v>-42.667259000000001</v>
+        <v>-42.692242</v>
       </c>
       <c r="D83" t="s">
         <v>28</v>
       </c>
       <c r="F83" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G83" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="B84">
-        <v>-25.656942000000001</v>
+        <v>-25.022000999999999</v>
       </c>
       <c r="C84">
-        <v>-42.858749000000003</v>
+        <v>-42.667259000000001</v>
       </c>
       <c r="D84" t="s">
         <v>28</v>
       </c>
       <c r="F84" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G84" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B85">
-        <v>-24.776168999999999</v>
+        <v>-25.656942000000001</v>
       </c>
       <c r="C85">
-        <v>-42.720005</v>
+        <v>-42.858749000000003</v>
       </c>
       <c r="D85" t="s">
         <v>28</v>
       </c>
       <c r="F85" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G85" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B86">
-        <v>-24.64</v>
+        <v>-24.951167999999999</v>
       </c>
       <c r="C86">
-        <v>-42.51</v>
+        <v>-42.467758000000003</v>
       </c>
       <c r="D86" t="s">
         <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G86" t="s">
-        <v>109</v>
+        <v>168</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B87">
-        <v>-24.78</v>
+        <v>-24.776168999999999</v>
       </c>
       <c r="C87">
-        <v>-42.5</v>
+        <v>-42.720005</v>
       </c>
       <c r="D87" t="s">
         <v>28</v>
       </c>
       <c r="F87" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G87" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B88">
-        <v>-24.68</v>
+        <v>-24.64</v>
       </c>
       <c r="C88">
-        <v>-42.5</v>
+        <v>-42.51</v>
       </c>
       <c r="D88" t="s">
         <v>28</v>
       </c>
       <c r="F88" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G88" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="B89">
-        <v>-24.63</v>
+        <v>37.594048000000001</v>
       </c>
       <c r="C89">
-        <v>-42.41</v>
+        <v>121.40307</v>
       </c>
       <c r="D89" t="s">
         <v>28</v>
       </c>
       <c r="F89" t="s">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="G89" t="s">
-        <v>109</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B90">
-        <v>-24.67</v>
+        <v>-24.78</v>
       </c>
       <c r="C90">
-        <v>-42.38</v>
+        <v>-42.5</v>
       </c>
       <c r="D90" t="s">
         <v>28</v>
       </c>
       <c r="F90" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G90" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B91">
-        <v>-24.54</v>
+        <v>-24.68</v>
       </c>
       <c r="C91">
-        <v>-42.46</v>
+        <v>-42.5</v>
       </c>
       <c r="D91" t="s">
         <v>28</v>
       </c>
       <c r="F91" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G91" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="B92">
-        <v>-24.59</v>
+        <v>-24.63</v>
       </c>
       <c r="C92">
-        <v>-42.56</v>
+        <v>-42.41</v>
       </c>
       <c r="D92" t="s">
         <v>28</v>
       </c>
       <c r="F92" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G92" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B93">
-        <v>-24.74</v>
+        <v>-24.67</v>
       </c>
       <c r="C93">
-        <v>-42.51</v>
+        <v>-42.38</v>
       </c>
       <c r="D93" t="s">
         <v>28</v>
       </c>
       <c r="F93" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G93" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="B94">
-        <v>-25.798373999999999</v>
+        <v>-24.54</v>
       </c>
       <c r="C94">
-        <v>-43.262680000000003</v>
+        <v>-42.46</v>
       </c>
       <c r="D94" t="s">
         <v>28</v>
       </c>
       <c r="F94" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G94" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B95">
-        <v>-25.671883000000001</v>
+        <v>-24.59</v>
       </c>
       <c r="C95">
-        <v>-43.205939999999998</v>
+        <v>-42.56</v>
       </c>
       <c r="D95" t="s">
         <v>28</v>
       </c>
       <c r="F95" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G95" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B96">
-        <v>-25.226118</v>
+        <v>-24.74</v>
       </c>
       <c r="C96">
-        <v>-42.56982</v>
+        <v>-42.51</v>
       </c>
       <c r="D96" t="s">
         <v>28</v>
       </c>
       <c r="F96" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G96" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B97">
-        <v>-24.685623</v>
+        <v>-25.798373999999999</v>
       </c>
       <c r="C97">
-        <v>-42.293922000000002</v>
+        <v>-43.262680000000003</v>
       </c>
       <c r="D97" t="s">
         <v>28</v>
       </c>
       <c r="F97" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G97" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B98">
-        <v>-22.1</v>
+        <v>-25.671883000000001</v>
       </c>
       <c r="C98">
-        <v>-39.909999999999997</v>
+        <v>-43.205939999999998</v>
       </c>
       <c r="D98" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F98" t="s">
-        <v>31</v>
+        <v>103</v>
+      </c>
+      <c r="G98" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B99">
-        <v>-23.08</v>
+        <v>-25.226118</v>
       </c>
       <c r="C99">
-        <v>-40.99</v>
+        <v>-42.56982</v>
       </c>
       <c r="D99" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="F99" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G99" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>119</v>
+        <v>112</v>
+      </c>
+      <c r="B100">
+        <v>-24.685623</v>
+      </c>
+      <c r="C100">
+        <v>-42.293922000000002</v>
       </c>
       <c r="D100" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="F100" t="s">
-        <v>31</v>
+        <v>103</v>
+      </c>
+      <c r="G100" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
+      </c>
+      <c r="B101">
+        <v>-22.1</v>
+      </c>
+      <c r="C101">
+        <v>-39.909999999999997</v>
+      </c>
+      <c r="D101" t="s">
+        <v>79</v>
       </c>
       <c r="F101" t="s">
         <v>31</v>
@@ -2776,33 +2863,30 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B102">
-        <v>-22.14</v>
+        <v>-23.08</v>
       </c>
       <c r="C102">
-        <v>-39.92</v>
+        <v>-40.99</v>
       </c>
       <c r="D102" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F102" t="s">
         <v>31</v>
+      </c>
+      <c r="G102" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B103">
-        <v>-22.14</v>
-      </c>
-      <c r="C103">
-        <v>-39.92</v>
+        <v>117</v>
       </c>
       <c r="D103" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="F103" t="s">
         <v>31</v>
@@ -2810,30 +2894,21 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B104">
-        <v>-23.3827</v>
-      </c>
-      <c r="C104">
-        <v>-40.073999999999998</v>
-      </c>
-      <c r="D104" t="s">
-        <v>24</v>
-      </c>
-      <c r="E104" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F104" t="s">
-        <v>105</v>
-      </c>
-      <c r="G104" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
+      </c>
+      <c r="B105">
+        <v>-22.14</v>
+      </c>
+      <c r="C105">
+        <v>-39.92</v>
       </c>
       <c r="D105" t="s">
         <v>24</v>
@@ -2842,87 +2917,138 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B106">
+        <v>-22.14</v>
+      </c>
+      <c r="C106">
+        <v>-39.92</v>
+      </c>
+      <c r="D106" t="s">
+        <v>24</v>
+      </c>
+      <c r="F106" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B107">
+        <v>-23.3827</v>
+      </c>
+      <c r="C107">
+        <v>-40.073999999999998</v>
+      </c>
+      <c r="D107" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107" t="s">
+        <v>123</v>
+      </c>
+      <c r="F107" t="s">
+        <v>103</v>
+      </c>
+      <c r="G107" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D108" t="s">
+        <v>24</v>
+      </c>
+      <c r="F108" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F109" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F110" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>128</v>
       </c>
-      <c r="F106" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
+      <c r="B111">
+        <v>-21.33</v>
+      </c>
+      <c r="C111">
+        <v>-40.049999999999997</v>
+      </c>
+      <c r="D111" t="s">
+        <v>28</v>
+      </c>
+      <c r="E111" t="s">
         <v>129</v>
       </c>
-      <c r="F107" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="F111" t="s">
         <v>130</v>
       </c>
-      <c r="B108">
-        <v>-21.33</v>
-      </c>
-      <c r="C108">
-        <v>-40.049999999999997</v>
-      </c>
-      <c r="D108" t="s">
-        <v>28</v>
-      </c>
-      <c r="E108" t="s">
-        <v>131</v>
-      </c>
-      <c r="F108" t="s">
-        <v>132</v>
-      </c>
-      <c r="G108" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
+      <c r="G111" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B112">
+        <v>-22.436900000000001</v>
+      </c>
+      <c r="C112">
+        <v>-40.425800000000002</v>
+      </c>
+      <c r="D112" t="s">
+        <v>49</v>
+      </c>
+      <c r="F112" t="s">
+        <v>31</v>
+      </c>
+      <c r="G112" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B109">
-        <v>-22.436900000000001</v>
-      </c>
-      <c r="C109">
-        <v>-40.425800000000002</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="B113">
+        <v>-22.374779</v>
+      </c>
+      <c r="C113">
+        <v>-40.417454999999997</v>
+      </c>
+      <c r="D113" t="s">
         <v>49</v>
       </c>
-      <c r="F109" t="s">
-        <v>31</v>
-      </c>
-      <c r="G109" t="s">
+      <c r="F113" t="s">
+        <v>31</v>
+      </c>
+      <c r="G113" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B110">
-        <v>-22.374779</v>
-      </c>
-      <c r="C110">
-        <v>-40.417454999999997</v>
-      </c>
-      <c r="D110" t="s">
-        <v>49</v>
-      </c>
-      <c r="F110" t="s">
-        <v>31</v>
-      </c>
-      <c r="G110" t="s">
-        <v>154</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G110" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G113" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/dados/SURVEY_POSICOES.xlsx
+++ b/dados/SURVEY_POSICOES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\OneDrive - cefet-rj.br\Empresas e entrevistas\projeto logistica offshore\ofi\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="8_{05B29B93-3891-4267-B1D3-244755FBEFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A650D45-937E-4FFB-809D-0F245D20853A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0AE550-2B79-4406-B979-0E61E97C2145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
@@ -3057,6 +3057,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A458B0-5351-487A-ABCF-BB5088AD3353}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+  </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
